--- a/database/event/8248/event_8248_evp_summary.xlsx
+++ b/database/event/8248/event_8248_evp_summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EVP_Summary_8248" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVP_Summary_8248" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,7 +502,7 @@
         <v>5.2111</v>
       </c>
       <c r="D2" t="n">
-        <v>2.775</v>
+        <v>3.1374</v>
       </c>
       <c r="E2" t="n">
         <v>8.8094</v>
@@ -548,7 +548,7 @@
         <v>4.9435</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6076</v>
+        <v>2.9547</v>
       </c>
       <c r="E3" t="n">
         <v>8.357100000000001</v>
@@ -594,7 +594,7 @@
         <v>4.6832</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4448</v>
+        <v>2.7769</v>
       </c>
       <c r="E4" t="n">
         <v>7.917</v>
@@ -640,7 +640,7 @@
         <v>3.9186</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9666</v>
+        <v>2.2548</v>
       </c>
       <c r="E5" t="n">
         <v>6.6245</v>
@@ -686,7 +686,7 @@
         <v>3.3012</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5804</v>
+        <v>1.8332</v>
       </c>
       <c r="E6" t="n">
         <v>5.5808</v>
@@ -732,7 +732,7 @@
         <v>2.7904</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2609</v>
+        <v>1.4843</v>
       </c>
       <c r="E7" t="n">
         <v>4.7172</v>
@@ -778,7 +778,7 @@
         <v>2.5329</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0998</v>
+        <v>1.3084</v>
       </c>
       <c r="E8" t="n">
         <v>4.2819</v>
@@ -824,7 +824,7 @@
         <v>2.5117</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0865</v>
+        <v>1.2939</v>
       </c>
       <c r="E9" t="n">
         <v>4.246</v>
@@ -870,7 +870,7 @@
         <v>2.48</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0667</v>
+        <v>1.2723</v>
       </c>
       <c r="E10" t="n">
         <v>4.1924</v>
@@ -916,7 +916,7 @@
         <v>2.3199</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9666</v>
+        <v>1.163</v>
       </c>
       <c r="E11" t="n">
         <v>3.9218</v>
@@ -962,7 +962,7 @@
         <v>2.1249</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8446</v>
+        <v>1.0298</v>
       </c>
       <c r="E12" t="n">
         <v>3.5922</v>
@@ -1008,7 +1008,7 @@
         <v>1.9915</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7612</v>
+        <v>0.9387</v>
       </c>
       <c r="E13" t="n">
         <v>3.3667</v>
@@ -1054,7 +1054,7 @@
         <v>1.8296</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6599</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="E14" t="n">
         <v>3.093</v>
@@ -1100,7 +1100,7 @@
         <v>1.7993</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6409</v>
+        <v>0.8074</v>
       </c>
       <c r="E15" t="n">
         <v>3.0417</v>
@@ -1146,7 +1146,7 @@
         <v>1.705</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5819</v>
+        <v>0.743</v>
       </c>
       <c r="E16" t="n">
         <v>2.8823</v>
@@ -1192,7 +1192,7 @@
         <v>1.6147</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5254</v>
+        <v>0.6813</v>
       </c>
       <c r="E17" t="n">
         <v>2.7296</v>
@@ -1238,7 +1238,7 @@
         <v>1.584</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5062</v>
+        <v>0.6604</v>
       </c>
       <c r="E18" t="n">
         <v>2.6777</v>
@@ -1284,7 +1284,7 @@
         <v>1.345</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3568</v>
+        <v>0.4972</v>
       </c>
       <c r="E19" t="n">
         <v>2.2738</v>
@@ -1330,7 +1330,7 @@
         <v>1.162</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2423</v>
+        <v>0.3722</v>
       </c>
       <c r="E20" t="n">
         <v>1.9643</v>
@@ -1376,7 +1376,7 @@
         <v>1.1365</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2264</v>
+        <v>0.3548</v>
       </c>
       <c r="E21" t="n">
         <v>1.9213</v>
@@ -1422,7 +1422,7 @@
         <v>1.0987</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2027</v>
+        <v>0.3289</v>
       </c>
       <c r="E22" t="n">
         <v>1.8573</v>
@@ -1468,7 +1468,7 @@
         <v>1.0067</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1452</v>
+        <v>0.2662</v>
       </c>
       <c r="E23" t="n">
         <v>1.7019</v>
@@ -1514,7 +1514,7 @@
         <v>0.8762</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0635</v>
+        <v>0.177</v>
       </c>
       <c r="E24" t="n">
         <v>1.4812</v>
@@ -1560,7 +1560,7 @@
         <v>0.8623</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0549</v>
+        <v>0.1676</v>
       </c>
       <c r="E25" t="n">
         <v>1.4578</v>
@@ -1606,7 +1606,7 @@
         <v>0.8372000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0391</v>
+        <v>0.1504</v>
       </c>
       <c r="E26" t="n">
         <v>1.4153</v>
@@ -1652,7 +1652,7 @@
         <v>0.7711</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0022</v>
+        <v>0.1053</v>
       </c>
       <c r="E27" t="n">
         <v>1.3036</v>
@@ -1698,7 +1698,7 @@
         <v>0.7508</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0149</v>
+        <v>0.0914</v>
       </c>
       <c r="E28" t="n">
         <v>1.2692</v>
@@ -1744,7 +1744,7 @@
         <v>0.7237</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0318</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="E29" t="n">
         <v>1.2235</v>
@@ -1790,7 +1790,7 @@
         <v>0.7050999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0435</v>
+        <v>0.0601</v>
       </c>
       <c r="E30" t="n">
         <v>1.1919</v>
@@ -1836,7 +1836,7 @@
         <v>0.6806</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0588</v>
+        <v>0.0435</v>
       </c>
       <c r="E31" t="n">
         <v>1.1506</v>
@@ -1882,7 +1882,7 @@
         <v>0.6199</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0968</v>
+        <v>0.002</v>
       </c>
       <c r="E32" t="n">
         <v>1.0479</v>
@@ -1928,7 +1928,7 @@
         <v>0.583</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1199</v>
+        <v>-0.0232</v>
       </c>
       <c r="E33" t="n">
         <v>0.9855</v>
@@ -1974,7 +1974,7 @@
         <v>0.5521</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1392</v>
+        <v>-0.0443</v>
       </c>
       <c r="E34" t="n">
         <v>0.9333</v>
@@ -2020,7 +2020,7 @@
         <v>0.5164</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1615</v>
+        <v>-0.0687</v>
       </c>
       <c r="E35" t="n">
         <v>0.8729</v>
@@ -2066,7 +2066,7 @@
         <v>0.4845</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1815</v>
+        <v>-0.0905</v>
       </c>
       <c r="E36" t="n">
         <v>0.819</v>
@@ -2112,7 +2112,7 @@
         <v>0.4616</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1958</v>
+        <v>-0.1061</v>
       </c>
       <c r="E37" t="n">
         <v>0.7804</v>
@@ -2158,7 +2158,7 @@
         <v>0.399</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2349</v>
+        <v>-0.1488</v>
       </c>
       <c r="E38" t="n">
         <v>0.6746</v>
@@ -2204,7 +2204,7 @@
         <v>0.3371</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2737</v>
+        <v>-0.1912</v>
       </c>
       <c r="E39" t="n">
         <v>0.5698</v>
@@ -2250,7 +2250,7 @@
         <v>0.3085</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2916</v>
+        <v>-0.2107</v>
       </c>
       <c r="E40" t="n">
         <v>0.5215</v>
@@ -2296,7 +2296,7 @@
         <v>0.3076</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2921</v>
+        <v>-0.2113</v>
       </c>
       <c r="E41" t="n">
         <v>0.52</v>
@@ -2342,7 +2342,7 @@
         <v>0.2847</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3064</v>
+        <v>-0.2269</v>
       </c>
       <c r="E42" t="n">
         <v>0.4813</v>
@@ -2388,7 +2388,7 @@
         <v>0.2728</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3139</v>
+        <v>-0.235</v>
       </c>
       <c r="E43" t="n">
         <v>0.4612</v>
@@ -2434,7 +2434,7 @@
         <v>0.2693</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3161</v>
+        <v>-0.2374</v>
       </c>
       <c r="E44" t="n">
         <v>0.4553</v>
@@ -2480,7 +2480,7 @@
         <v>0.2109</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3526</v>
+        <v>-0.2773</v>
       </c>
       <c r="E45" t="n">
         <v>0.3565</v>
@@ -2526,7 +2526,7 @@
         <v>0.2064</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3554</v>
+        <v>-0.2804</v>
       </c>
       <c r="E46" t="n">
         <v>0.349</v>
@@ -2572,7 +2572,7 @@
         <v>0.1201</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4094</v>
+        <v>-0.3393</v>
       </c>
       <c r="E47" t="n">
         <v>0.2031</v>
@@ -2618,7 +2618,7 @@
         <v>0.0596</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4472</v>
+        <v>-0.3806</v>
       </c>
       <c r="E48" t="n">
         <v>0.1008</v>
@@ -2664,7 +2664,7 @@
         <v>0.0422</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4581</v>
+        <v>-0.3925</v>
       </c>
       <c r="E49" t="n">
         <v>0.07140000000000001</v>
@@ -2710,7 +2710,7 @@
         <v>0.022</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4708</v>
+        <v>-0.4063</v>
       </c>
       <c r="E50" t="n">
         <v>0.0372</v>
@@ -2756,7 +2756,7 @@
         <v>0.0119</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4771</v>
+        <v>-0.4132</v>
       </c>
       <c r="E51" t="n">
         <v>0.0201</v>
@@ -2802,7 +2802,7 @@
         <v>-0.0043</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4872</v>
+        <v>-0.4243</v>
       </c>
       <c r="E52" t="n">
         <v>-0.0072</v>
@@ -2848,7 +2848,7 @@
         <v>-0.0221</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4984</v>
+        <v>-0.4365</v>
       </c>
       <c r="E53" t="n">
         <v>-0.0374</v>
@@ -2894,7 +2894,7 @@
         <v>-0.048</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.4542</v>
       </c>
       <c r="E54" t="n">
         <v>-0.08119999999999999</v>
@@ -2940,7 +2940,7 @@
         <v>-0.0697</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5281</v>
+        <v>-0.469</v>
       </c>
       <c r="E55" t="n">
         <v>-0.1179</v>
@@ -2986,7 +2986,7 @@
         <v>-0.07770000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5331</v>
+        <v>-0.4744</v>
       </c>
       <c r="E56" t="n">
         <v>-0.1313</v>
@@ -3032,7 +3032,7 @@
         <v>-0.08169999999999999</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5356</v>
+        <v>-0.4772</v>
       </c>
       <c r="E57" t="n">
         <v>-0.1381</v>
@@ -3078,7 +3078,7 @@
         <v>-0.08550000000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.538</v>
+        <v>-0.4797</v>
       </c>
       <c r="E58" t="n">
         <v>-0.1445</v>
@@ -3124,7 +3124,7 @@
         <v>-0.1416</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.518</v>
       </c>
       <c r="E59" t="n">
         <v>-0.2393</v>
@@ -3170,7 +3170,7 @@
         <v>-0.1524</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5799</v>
+        <v>-0.5255</v>
       </c>
       <c r="E60" t="n">
         <v>-0.2577</v>
@@ -3216,7 +3216,7 @@
         <v>-0.1615</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5856</v>
+        <v>-0.5317</v>
       </c>
       <c r="E61" t="n">
         <v>-0.2731</v>
@@ -3262,7 +3262,7 @@
         <v>-0.2454</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.638</v>
+        <v>-0.589</v>
       </c>
       <c r="E62" t="n">
         <v>-0.4149</v>
@@ -3308,7 +3308,7 @@
         <v>-0.315</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6815</v>
+        <v>-0.6365</v>
       </c>
       <c r="E63" t="n">
         <v>-0.5325</v>
@@ -3354,7 +3354,7 @@
         <v>-0.3347</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6939</v>
+        <v>-0.6499</v>
       </c>
       <c r="E64" t="n">
         <v>-0.5658</v>
@@ -3400,7 +3400,7 @@
         <v>-0.3686</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7151</v>
+        <v>-0.6731</v>
       </c>
       <c r="E65" t="n">
         <v>-0.6232</v>
@@ -3446,7 +3446,7 @@
         <v>-0.3979</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-0.6931</v>
       </c>
       <c r="E66" t="n">
         <v>-0.6727</v>
@@ -3492,7 +3492,7 @@
         <v>-0.4423</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7612</v>
+        <v>-0.7234</v>
       </c>
       <c r="E67" t="n">
         <v>-0.7477</v>
@@ -3538,7 +3538,7 @@
         <v>-0.5206</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8102</v>
+        <v>-0.7769</v>
       </c>
       <c r="E68" t="n">
         <v>-0.8801</v>
@@ -3584,7 +3584,7 @@
         <v>-0.5436</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8245</v>
+        <v>-0.7926</v>
       </c>
       <c r="E69" t="n">
         <v>-0.9189000000000001</v>
@@ -3630,7 +3630,7 @@
         <v>-0.6074000000000001</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="E70" t="n">
         <v>-1.0268</v>
@@ -3676,7 +3676,7 @@
         <v>-0.6101</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8661</v>
+        <v>-0.838</v>
       </c>
       <c r="E71" t="n">
         <v>-1.0314</v>
@@ -3722,7 +3722,7 @@
         <v>-0.6953</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9194</v>
+        <v>-0.8962</v>
       </c>
       <c r="E72" t="n">
         <v>-1.1754</v>
@@ -3768,7 +3768,7 @@
         <v>-0.7789</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9717</v>
+        <v>-0.9533</v>
       </c>
       <c r="E73" t="n">
         <v>-1.3168</v>
@@ -3814,7 +3814,7 @@
         <v>-0.7966</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9828</v>
+        <v>-0.9654</v>
       </c>
       <c r="E74" t="n">
         <v>-1.3466</v>
@@ -3860,7 +3860,7 @@
         <v>-0.8801</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.035</v>
+        <v>-1.0224</v>
       </c>
       <c r="E75" t="n">
         <v>-1.4878</v>
@@ -3906,7 +3906,7 @@
         <v>-0.9702</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0914</v>
+        <v>-1.0839</v>
       </c>
       <c r="E76" t="n">
         <v>-1.6401</v>
@@ -3952,7 +3952,7 @@
         <v>-1.0141</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1188</v>
+        <v>-1.1139</v>
       </c>
       <c r="E77" t="n">
         <v>-1.7144</v>
@@ -3998,7 +3998,7 @@
         <v>-1.0975</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.171</v>
+        <v>-1.1709</v>
       </c>
       <c r="E78" t="n">
         <v>-1.8554</v>
@@ -4044,7 +4044,7 @@
         <v>-1.4746</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.4069</v>
+        <v>-1.4284</v>
       </c>
       <c r="E79" t="n">
         <v>-2.4928</v>
@@ -4090,7 +4090,7 @@
         <v>-1.516</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.4328</v>
+        <v>-1.4567</v>
       </c>
       <c r="E80" t="n">
         <v>-2.5629</v>
@@ -4136,7 +4136,7 @@
         <v>-1.8866</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.6646</v>
+        <v>-1.7098</v>
       </c>
       <c r="E81" t="n">
         <v>-3.1894</v>
@@ -4182,7 +4182,7 @@
         <v>-2.2396</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.8854</v>
+        <v>-1.9509</v>
       </c>
       <c r="E82" t="n">
         <v>-3.7861</v>

--- a/database/event/8248/event_8248_evp_summary.xlsx
+++ b/database/event/8248/event_8248_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>5.2111</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1374</v>
+        <v>3.0658</v>
       </c>
       <c r="E2" t="n">
         <v>8.8094</v>
@@ -548,7 +548,7 @@
         <v>4.9435</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9547</v>
+        <v>2.8856</v>
       </c>
       <c r="E3" t="n">
         <v>8.357100000000001</v>
@@ -594,7 +594,7 @@
         <v>4.6832</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7769</v>
+        <v>2.7102</v>
       </c>
       <c r="E4" t="n">
         <v>7.917</v>
@@ -640,7 +640,7 @@
         <v>3.9186</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2548</v>
+        <v>2.1953</v>
       </c>
       <c r="E5" t="n">
         <v>6.6245</v>
@@ -686,7 +686,7 @@
         <v>3.3012</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8332</v>
+        <v>1.7795</v>
       </c>
       <c r="E6" t="n">
         <v>5.5808</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.7172</v>
+        <v>4.7051</v>
       </c>
       <c r="C7" t="n">
-        <v>2.7904</v>
+        <v>2.7832</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4843</v>
+        <v>1.4306</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7172</v>
+        <v>4.7051</v>
       </c>
       <c r="F7" t="n">
-        <v>4.7172</v>
+        <v>4.7051</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>5.0936</v>
+        <v>5.0746</v>
       </c>
       <c r="I7" t="n">
         <v>5.1173</v>
@@ -778,7 +778,7 @@
         <v>2.5329</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3084</v>
+        <v>1.262</v>
       </c>
       <c r="E8" t="n">
         <v>4.2819</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.246</v>
+        <v>4.2157</v>
       </c>
       <c r="C9" t="n">
-        <v>2.5117</v>
+        <v>2.4937</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2939</v>
+        <v>1.2356</v>
       </c>
       <c r="E9" t="n">
-        <v>4.246</v>
+        <v>4.2157</v>
       </c>
       <c r="F9" t="n">
-        <v>4.1837</v>
+        <v>4.1534</v>
       </c>
       <c r="G9" t="n">
         <v>0.0623</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2569</v>
+        <v>4.2095</v>
       </c>
       <c r="I9" t="n">
         <v>4.3167</v>
@@ -870,7 +870,7 @@
         <v>2.48</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2723</v>
+        <v>1.2263</v>
       </c>
       <c r="E10" t="n">
         <v>4.1924</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.9218</v>
+        <v>3.8815</v>
       </c>
       <c r="C11" t="n">
-        <v>2.3199</v>
+        <v>2.296</v>
       </c>
       <c r="D11" t="n">
-        <v>1.163</v>
+        <v>1.1025</v>
       </c>
       <c r="E11" t="n">
-        <v>3.9218</v>
+        <v>3.8815</v>
       </c>
       <c r="F11" t="n">
-        <v>3.6203</v>
+        <v>3.58</v>
       </c>
       <c r="G11" t="n">
         <v>0.3015</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6203</v>
+        <v>3.58</v>
       </c>
       <c r="I11" t="n">
         <v>3.6711</v>
@@ -962,7 +962,7 @@
         <v>2.1249</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0298</v>
+        <v>0.9872</v>
       </c>
       <c r="E12" t="n">
         <v>3.5922</v>
@@ -1008,7 +1008,7 @@
         <v>1.9915</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9387</v>
+        <v>0.8974</v>
       </c>
       <c r="E13" t="n">
         <v>3.3667</v>
@@ -1054,7 +1054,7 @@
         <v>1.8296</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.7883</v>
       </c>
       <c r="E14" t="n">
         <v>3.093</v>
@@ -1100,7 +1100,7 @@
         <v>1.7993</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8074</v>
+        <v>0.7679</v>
       </c>
       <c r="E15" t="n">
         <v>3.0417</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.8823</v>
+        <v>2.8756</v>
       </c>
       <c r="C16" t="n">
-        <v>1.705</v>
+        <v>1.701</v>
       </c>
       <c r="D16" t="n">
-        <v>0.743</v>
+        <v>0.7017</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8823</v>
+        <v>2.8756</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8054</v>
+        <v>1.7987</v>
       </c>
       <c r="G16" t="n">
         <v>1.0769</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8054</v>
+        <v>1.7987</v>
       </c>
       <c r="I16" t="n">
         <v>1.8138</v>
@@ -1192,7 +1192,7 @@
         <v>1.6147</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6813</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="E17" t="n">
         <v>2.7296</v>
@@ -1238,7 +1238,7 @@
         <v>1.584</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6604</v>
+        <v>0.6229</v>
       </c>
       <c r="E18" t="n">
         <v>2.6777</v>
@@ -1284,7 +1284,7 @@
         <v>1.345</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4972</v>
+        <v>0.462</v>
       </c>
       <c r="E19" t="n">
         <v>2.2738</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.9643</v>
+        <v>1.951</v>
       </c>
       <c r="C20" t="n">
-        <v>1.162</v>
+        <v>1.1541</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3722</v>
+        <v>0.3334</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9643</v>
+        <v>1.951</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7813</v>
+        <v>1.768</v>
       </c>
       <c r="G20" t="n">
         <v>0.183</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7813</v>
+        <v>1.768</v>
       </c>
       <c r="I20" t="n">
         <v>1.7979</v>
@@ -1376,7 +1376,7 @@
         <v>1.1365</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3548</v>
+        <v>0.3215</v>
       </c>
       <c r="E21" t="n">
         <v>1.9213</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.8573</v>
+        <v>1.843</v>
       </c>
       <c r="C22" t="n">
-        <v>1.0987</v>
+        <v>1.0902</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3289</v>
+        <v>0.2903</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8573</v>
+        <v>1.843</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9247</v>
+        <v>1.9104</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0674</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9247</v>
+        <v>1.9104</v>
       </c>
       <c r="I22" t="n">
         <v>1.9427</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.7019</v>
+        <v>1.6818</v>
       </c>
       <c r="C23" t="n">
-        <v>1.0067</v>
+        <v>0.9948</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2662</v>
+        <v>0.2261</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7019</v>
+        <v>1.6818</v>
       </c>
       <c r="F23" t="n">
-        <v>2.7019</v>
+        <v>2.6818</v>
       </c>
       <c r="G23" t="n">
         <v>-1</v>
       </c>
       <c r="H23" t="n">
-        <v>2.7019</v>
+        <v>2.6818</v>
       </c>
       <c r="I23" t="n">
         <v>2.7271</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.4812</v>
+        <v>1.4757</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8762</v>
+        <v>0.8729</v>
       </c>
       <c r="D24" t="n">
-        <v>0.177</v>
+        <v>0.144</v>
       </c>
       <c r="E24" t="n">
-        <v>1.4812</v>
+        <v>1.4757</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4812</v>
+        <v>1.4757</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.4812</v>
+        <v>1.4757</v>
       </c>
       <c r="I24" t="n">
         <v>1.4881</v>
@@ -1560,7 +1560,7 @@
         <v>0.8623</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1676</v>
+        <v>0.1369</v>
       </c>
       <c r="E25" t="n">
         <v>1.4578</v>
@@ -1606,7 +1606,7 @@
         <v>0.8372000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1504</v>
+        <v>0.1199</v>
       </c>
       <c r="E26" t="n">
         <v>1.4153</v>
@@ -1652,7 +1652,7 @@
         <v>0.7711</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1053</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="E27" t="n">
         <v>1.3036</v>
@@ -1698,7 +1698,7 @@
         <v>0.7508</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0914</v>
+        <v>0.0617</v>
       </c>
       <c r="E28" t="n">
         <v>1.2692</v>
@@ -1744,7 +1744,7 @@
         <v>0.7237</v>
       </c>
       <c r="D29" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0435</v>
       </c>
       <c r="E29" t="n">
         <v>1.2235</v>
@@ -1790,7 +1790,7 @@
         <v>0.7050999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0601</v>
+        <v>0.0309</v>
       </c>
       <c r="E30" t="n">
         <v>1.1919</v>
@@ -1836,7 +1836,7 @@
         <v>0.6806</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0435</v>
+        <v>0.0145</v>
       </c>
       <c r="E31" t="n">
         <v>1.1506</v>
@@ -1882,7 +1882,7 @@
         <v>0.6199</v>
       </c>
       <c r="D32" t="n">
-        <v>0.002</v>
+        <v>-0.0264</v>
       </c>
       <c r="E32" t="n">
         <v>1.0479</v>
@@ -1928,7 +1928,7 @@
         <v>0.583</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0232</v>
+        <v>-0.0513</v>
       </c>
       <c r="E33" t="n">
         <v>0.9855</v>
@@ -1974,7 +1974,7 @@
         <v>0.5521</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0443</v>
+        <v>-0.0721</v>
       </c>
       <c r="E34" t="n">
         <v>0.9333</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8729</v>
+        <v>0.8696</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5164</v>
+        <v>0.5144</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0687</v>
+        <v>-0.0975</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8729</v>
+        <v>0.8696</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8729</v>
+        <v>0.8696</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8729</v>
+        <v>0.8696</v>
       </c>
       <c r="I35" t="n">
         <v>0.877</v>
@@ -2066,7 +2066,7 @@
         <v>0.4845</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0905</v>
+        <v>-0.1176</v>
       </c>
       <c r="E36" t="n">
         <v>0.819</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7804</v>
+        <v>0.7607</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4616</v>
+        <v>0.45</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1061</v>
+        <v>-0.1408</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7804</v>
+        <v>0.7607</v>
       </c>
       <c r="F37" t="n">
-        <v>1.766</v>
+        <v>1.7463</v>
       </c>
       <c r="G37" t="n">
         <v>-0.9856</v>
       </c>
       <c r="H37" t="n">
-        <v>1.766</v>
+        <v>1.7463</v>
       </c>
       <c r="I37" t="n">
         <v>1.7908</v>
@@ -2158,7 +2158,7 @@
         <v>0.399</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1488</v>
+        <v>-0.1751</v>
       </c>
       <c r="E38" t="n">
         <v>0.6746</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5698</v>
+        <v>0.5677</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3371</v>
+        <v>0.3358</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1912</v>
+        <v>-0.2177</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5698</v>
+        <v>0.5677</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5698</v>
+        <v>0.5677</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5698</v>
+        <v>0.5677</v>
       </c>
       <c r="I39" t="n">
         <v>0.5725</v>
@@ -2250,7 +2250,7 @@
         <v>0.3085</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2107</v>
+        <v>-0.2361</v>
       </c>
       <c r="E40" t="n">
         <v>0.5215</v>
@@ -2296,7 +2296,7 @@
         <v>0.3076</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2113</v>
+        <v>-0.2367</v>
       </c>
       <c r="E41" t="n">
         <v>0.52</v>
@@ -2342,7 +2342,7 @@
         <v>0.2847</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2269</v>
+        <v>-0.2522</v>
       </c>
       <c r="E42" t="n">
         <v>0.4813</v>
@@ -2388,7 +2388,7 @@
         <v>0.2728</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.235</v>
+        <v>-0.2602</v>
       </c>
       <c r="E43" t="n">
         <v>0.4612</v>
@@ -2434,7 +2434,7 @@
         <v>0.2693</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2374</v>
+        <v>-0.2625</v>
       </c>
       <c r="E44" t="n">
         <v>0.4553</v>
@@ -2480,7 +2480,7 @@
         <v>0.2109</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2773</v>
+        <v>-0.3019</v>
       </c>
       <c r="E45" t="n">
         <v>0.3565</v>
@@ -2526,7 +2526,7 @@
         <v>0.2064</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2804</v>
+        <v>-0.3049</v>
       </c>
       <c r="E46" t="n">
         <v>0.349</v>
@@ -2572,7 +2572,7 @@
         <v>0.1201</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3393</v>
+        <v>-0.363</v>
       </c>
       <c r="E47" t="n">
         <v>0.2031</v>
@@ -2618,7 +2618,7 @@
         <v>0.0596</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3806</v>
+        <v>-0.4038</v>
       </c>
       <c r="E48" t="n">
         <v>0.1008</v>
@@ -2664,7 +2664,7 @@
         <v>0.0422</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3925</v>
+        <v>-0.4155</v>
       </c>
       <c r="E49" t="n">
         <v>0.07140000000000001</v>
@@ -2710,7 +2710,7 @@
         <v>0.022</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4063</v>
+        <v>-0.4291</v>
       </c>
       <c r="E50" t="n">
         <v>0.0372</v>
@@ -2756,7 +2756,7 @@
         <v>0.0119</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4132</v>
+        <v>-0.4359</v>
       </c>
       <c r="E51" t="n">
         <v>0.0201</v>
@@ -2802,7 +2802,7 @@
         <v>-0.0043</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4243</v>
+        <v>-0.4468</v>
       </c>
       <c r="E52" t="n">
         <v>-0.0072</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.0374</v>
+        <v>-0.0428</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0221</v>
+        <v>-0.0253</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4365</v>
+        <v>-0.461</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0374</v>
+        <v>-0.0428</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4849</v>
+        <v>0.4795</v>
       </c>
       <c r="G53" t="n">
         <v>-0.5223</v>
       </c>
       <c r="H53" t="n">
-        <v>0.4849</v>
+        <v>0.4795</v>
       </c>
       <c r="I53" t="n">
         <v>0.4917</v>
@@ -2894,7 +2894,7 @@
         <v>-0.048</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4542</v>
+        <v>-0.4763</v>
       </c>
       <c r="E54" t="n">
         <v>-0.08119999999999999</v>
@@ -2940,7 +2940,7 @@
         <v>-0.0697</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.469</v>
+        <v>-0.4909</v>
       </c>
       <c r="E55" t="n">
         <v>-0.1179</v>
@@ -2986,7 +2986,7 @@
         <v>-0.07770000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4744</v>
+        <v>-0.4962</v>
       </c>
       <c r="E56" t="n">
         <v>-0.1313</v>
@@ -3032,7 +3032,7 @@
         <v>-0.08169999999999999</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4772</v>
+        <v>-0.4989</v>
       </c>
       <c r="E57" t="n">
         <v>-0.1381</v>
@@ -3078,7 +3078,7 @@
         <v>-0.08550000000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4797</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="E58" t="n">
         <v>-0.1445</v>
@@ -3124,7 +3124,7 @@
         <v>-0.1416</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.518</v>
+        <v>-0.5392</v>
       </c>
       <c r="E59" t="n">
         <v>-0.2393</v>
@@ -3170,7 +3170,7 @@
         <v>-0.1524</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5255</v>
+        <v>-0.5466</v>
       </c>
       <c r="E60" t="n">
         <v>-0.2577</v>
@@ -3216,7 +3216,7 @@
         <v>-0.1615</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5317</v>
+        <v>-0.5527</v>
       </c>
       <c r="E61" t="n">
         <v>-0.2731</v>
@@ -3262,7 +3262,7 @@
         <v>-0.2454</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.589</v>
+        <v>-0.6092</v>
       </c>
       <c r="E62" t="n">
         <v>-0.4149</v>
@@ -3308,7 +3308,7 @@
         <v>-0.315</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6365</v>
+        <v>-0.6561</v>
       </c>
       <c r="E63" t="n">
         <v>-0.5325</v>
@@ -3354,7 +3354,7 @@
         <v>-0.3347</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6499</v>
+        <v>-0.6693</v>
       </c>
       <c r="E64" t="n">
         <v>-0.5658</v>
@@ -3400,7 +3400,7 @@
         <v>-0.3686</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6731</v>
+        <v>-0.6922</v>
       </c>
       <c r="E65" t="n">
         <v>-0.6232</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.6727</v>
+        <v>-0.6721</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.3979</v>
+        <v>-0.3976</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.6931</v>
+        <v>-0.7117</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.6727</v>
+        <v>-0.6721</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.0801</v>
       </c>
       <c r="G66" t="n">
         <v>-0.592</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.0801</v>
       </c>
       <c r="I66" t="n">
         <v>-0.0815</v>
@@ -3492,7 +3492,7 @@
         <v>-0.4423</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7234</v>
+        <v>-0.7418</v>
       </c>
       <c r="E67" t="n">
         <v>-0.7477</v>
@@ -3538,7 +3538,7 @@
         <v>-0.5206</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7769</v>
+        <v>-0.7945</v>
       </c>
       <c r="E68" t="n">
         <v>-0.8801</v>
@@ -3578,25 +3578,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.9189000000000001</v>
+        <v>-0.9155</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.5436</v>
+        <v>-0.5416</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7926</v>
+        <v>-0.8086</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.9189000000000001</v>
+        <v>-0.9155</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.9189000000000001</v>
+        <v>-0.9155</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.9189000000000001</v>
+        <v>-0.9155</v>
       </c>
       <c r="I69" t="n">
         <v>-0.9232</v>
@@ -3630,7 +3630,7 @@
         <v>-0.6074000000000001</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8362000000000001</v>
+        <v>-0.853</v>
       </c>
       <c r="E70" t="n">
         <v>-1.0268</v>
@@ -3676,7 +3676,7 @@
         <v>-0.6101</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.838</v>
+        <v>-0.8548</v>
       </c>
       <c r="E71" t="n">
         <v>-1.0314</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.1754</v>
+        <v>-1.1641</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.6953</v>
+        <v>-0.6886</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8962</v>
+        <v>-0.9077</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.1754</v>
+        <v>-1.1641</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.5275</v>
+        <v>-1.5162</v>
       </c>
       <c r="G72" t="n">
         <v>0.3521</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.5275</v>
+        <v>-1.5162</v>
       </c>
       <c r="I72" t="n">
         <v>-1.5418</v>
@@ -3768,7 +3768,7 @@
         <v>-0.7789</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9533</v>
+        <v>-0.9685</v>
       </c>
       <c r="E73" t="n">
         <v>-1.3168</v>
@@ -3814,7 +3814,7 @@
         <v>-0.7966</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9654</v>
+        <v>-0.9804</v>
       </c>
       <c r="E74" t="n">
         <v>-1.3466</v>
@@ -3860,7 +3860,7 @@
         <v>-0.8801</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0224</v>
+        <v>-1.0367</v>
       </c>
       <c r="E75" t="n">
         <v>-1.4878</v>
@@ -3906,7 +3906,7 @@
         <v>-0.9702</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0839</v>
+        <v>-1.0973</v>
       </c>
       <c r="E76" t="n">
         <v>-1.6401</v>
@@ -3952,7 +3952,7 @@
         <v>-1.0141</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1139</v>
+        <v>-1.1269</v>
       </c>
       <c r="E77" t="n">
         <v>-1.7144</v>
@@ -3998,7 +3998,7 @@
         <v>-1.0975</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1709</v>
+        <v>-1.1831</v>
       </c>
       <c r="E78" t="n">
         <v>-1.8554</v>
@@ -4044,7 +4044,7 @@
         <v>-1.4746</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.4284</v>
+        <v>-1.437</v>
       </c>
       <c r="E79" t="n">
         <v>-2.4928</v>
@@ -4090,7 +4090,7 @@
         <v>-1.516</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.4567</v>
+        <v>-1.465</v>
       </c>
       <c r="E80" t="n">
         <v>-2.5629</v>
@@ -4136,7 +4136,7 @@
         <v>-1.8866</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.7098</v>
+        <v>-1.7146</v>
       </c>
       <c r="E81" t="n">
         <v>-3.1894</v>
@@ -4182,7 +4182,7 @@
         <v>-2.2396</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.9509</v>
+        <v>-1.9523</v>
       </c>
       <c r="E82" t="n">
         <v>-3.7861</v>

--- a/database/event/8248/event_8248_evp_summary.xlsx
+++ b/database/event/8248/event_8248_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.501300000000001</v>
+        <v>8.7056</v>
       </c>
       <c r="C2" t="n">
-        <v>5.0288</v>
+        <v>5.1497</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2458</v>
+        <v>3.2748</v>
       </c>
       <c r="E2" t="n">
-        <v>8.501300000000001</v>
+        <v>8.7056</v>
       </c>
       <c r="F2" t="n">
-        <v>2.815</v>
+        <v>2.8074</v>
       </c>
       <c r="G2" t="n">
         <v>5.6863</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3936</v>
+        <v>4.3686</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3725</v>
+        <v>2.359</v>
       </c>
       <c r="J2" t="n">
         <v>5.6863</v>
@@ -529,7 +529,7 @@
         <v>102</v>
       </c>
       <c r="M2" t="n">
-        <v>8.0588</v>
+        <v>8.045300000000001</v>
       </c>
       <c r="N2" t="n">
         <v>232</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.7783</v>
+        <v>8.1349</v>
       </c>
       <c r="C3" t="n">
-        <v>4.6011</v>
+        <v>4.8121</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9166</v>
+        <v>3.0199</v>
       </c>
       <c r="E3" t="n">
-        <v>7.7783</v>
+        <v>8.1349</v>
       </c>
       <c r="F3" t="n">
         <v>4.5807</v>
@@ -560,10 +560,10 @@
         <v>3.1976</v>
       </c>
       <c r="H3" t="n">
-        <v>14.2339</v>
+        <v>14.2345</v>
       </c>
       <c r="I3" t="n">
-        <v>7.6862</v>
+        <v>7.6865</v>
       </c>
       <c r="J3" t="n">
         <v>3.1976</v>
@@ -575,7 +575,7 @@
         <v>102</v>
       </c>
       <c r="M3" t="n">
-        <v>10.8838</v>
+        <v>10.8841</v>
       </c>
       <c r="N3" t="n">
         <v>232</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.5791</v>
+        <v>7.8812</v>
       </c>
       <c r="C4" t="n">
-        <v>4.4833</v>
+        <v>4.662</v>
       </c>
       <c r="D4" t="n">
-        <v>2.826</v>
+        <v>2.9065</v>
       </c>
       <c r="E4" t="n">
-        <v>7.5791</v>
+        <v>7.8812</v>
       </c>
       <c r="F4" t="n">
         <v>4.5807</v>
@@ -606,10 +606,10 @@
         <v>2.9984</v>
       </c>
       <c r="H4" t="n">
-        <v>12.5411</v>
+        <v>12.5207</v>
       </c>
       <c r="I4" t="n">
-        <v>6.7721</v>
+        <v>6.7611</v>
       </c>
       <c r="J4" t="n">
         <v>2.9984</v>
@@ -621,7 +621,7 @@
         <v>102</v>
       </c>
       <c r="M4" t="n">
-        <v>9.7705</v>
+        <v>9.759499999999999</v>
       </c>
       <c r="N4" t="n">
         <v>232</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.3365</v>
+        <v>6.5986</v>
       </c>
       <c r="C5" t="n">
-        <v>3.7483</v>
+        <v>3.9033</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2603</v>
+        <v>2.3336</v>
       </c>
       <c r="E5" t="n">
-        <v>6.3365</v>
+        <v>6.5986</v>
       </c>
       <c r="F5" t="n">
         <v>4.5807</v>
@@ -652,10 +652,10 @@
         <v>1.7558</v>
       </c>
       <c r="H5" t="n">
-        <v>12.3741</v>
+        <v>12.3561</v>
       </c>
       <c r="I5" t="n">
-        <v>6.6819</v>
+        <v>6.6722</v>
       </c>
       <c r="J5" t="n">
         <v>1.7558</v>
@@ -667,7 +667,7 @@
         <v>131</v>
       </c>
       <c r="M5" t="n">
-        <v>8.4377</v>
+        <v>8.428000000000001</v>
       </c>
       <c r="N5" t="n">
         <v>319</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.56</v>
+        <v>6.2273</v>
       </c>
       <c r="C6" t="n">
-        <v>3.2889</v>
+        <v>3.6837</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9068</v>
+        <v>2.1678</v>
       </c>
       <c r="E6" t="n">
-        <v>5.56</v>
+        <v>6.2273</v>
       </c>
       <c r="F6" t="n">
-        <v>5.56</v>
+        <v>5.5596</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>9.444100000000001</v>
+        <v>9.443300000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>9.444100000000001</v>
+        <v>9.443300000000001</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>9.444100000000001</v>
+        <v>9.443300000000001</v>
       </c>
       <c r="N6" t="n">
         <v>166</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1106</v>
+        <v>4.2032</v>
       </c>
       <c r="C7" t="n">
-        <v>2.4316</v>
+        <v>2.4863</v>
       </c>
       <c r="D7" t="n">
-        <v>1.247</v>
+        <v>1.2637</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1106</v>
+        <v>4.2032</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5091</v>
+        <v>2.5094</v>
       </c>
       <c r="G7" t="n">
         <v>1.6015</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7667</v>
+        <v>2.7673</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7667</v>
+        <v>2.7673</v>
       </c>
       <c r="J7" t="n">
         <v>1.6015</v>
@@ -759,7 +759,7 @@
         <v>77</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3682</v>
+        <v>4.3688</v>
       </c>
       <c r="N7" t="n">
         <v>238</v>
@@ -768,231 +768,231 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0755</v>
+        <v>4.0794</v>
       </c>
       <c r="C8" t="n">
-        <v>2.4108</v>
+        <v>2.4131</v>
       </c>
       <c r="D8" t="n">
-        <v>1.231</v>
+        <v>1.2084</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0755</v>
+        <v>4.0794</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1834</v>
+        <v>3.7835</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8921</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1834</v>
+        <v>5.5559</v>
       </c>
       <c r="I8" t="n">
-        <v>0.639</v>
+        <v>5.6991</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8921</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="L8" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5311</v>
+        <v>5.6991</v>
       </c>
       <c r="N8" t="n">
-        <v>319</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BELCHONOKK</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.861</v>
+        <v>3.9982</v>
       </c>
       <c r="C9" t="n">
-        <v>2.2839</v>
+        <v>2.3651</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1334</v>
+        <v>1.1721</v>
       </c>
       <c r="E9" t="n">
-        <v>3.861</v>
+        <v>3.9982</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3349</v>
+        <v>1.1448</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5261</v>
+        <v>2.8921</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3854</v>
+        <v>1.1448</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3854</v>
+        <v>0.6182</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5261</v>
+        <v>2.8921</v>
       </c>
       <c r="K9" t="n">
-        <v>151</v>
+        <v>188</v>
       </c>
       <c r="L9" t="n">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9115</v>
+        <v>3.5103</v>
       </c>
       <c r="N9" t="n">
-        <v>263</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>kyousuke</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.8219</v>
+        <v>3.9569</v>
       </c>
       <c r="C10" t="n">
-        <v>2.2608</v>
+        <v>2.3406</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1156</v>
+        <v>1.1536</v>
       </c>
       <c r="E10" t="n">
-        <v>3.8219</v>
+        <v>3.9569</v>
       </c>
       <c r="F10" t="n">
-        <v>3.8482</v>
+        <v>2.578</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0263</v>
+        <v>1.119</v>
       </c>
       <c r="H10" t="n">
-        <v>7.8025</v>
+        <v>2.9174</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2133</v>
+        <v>2.9926</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0263</v>
+        <v>1.119</v>
       </c>
       <c r="K10" t="n">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="L10" t="n">
-        <v>131</v>
+        <v>47</v>
       </c>
       <c r="M10" t="n">
-        <v>4.187</v>
+        <v>4.1116</v>
       </c>
       <c r="N10" t="n">
-        <v>319</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.7835</v>
+        <v>3.9036</v>
       </c>
       <c r="C11" t="n">
-        <v>2.2381</v>
+        <v>2.3091</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0981</v>
+        <v>1.1298</v>
       </c>
       <c r="E11" t="n">
-        <v>3.7835</v>
+        <v>3.9036</v>
       </c>
       <c r="F11" t="n">
-        <v>3.7835</v>
+        <v>3.8324</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0.0263</v>
       </c>
       <c r="H11" t="n">
-        <v>5.5559</v>
+        <v>7.7503</v>
       </c>
       <c r="I11" t="n">
-        <v>5.6991</v>
+        <v>4.1851</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.0263</v>
       </c>
       <c r="K11" t="n">
-        <v>228</v>
+        <v>188</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="M11" t="n">
-        <v>5.6991</v>
+        <v>4.1588</v>
       </c>
       <c r="N11" t="n">
-        <v>228</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kyousuke</t>
+          <t>BELCHONOKK</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.6922</v>
+        <v>3.8406</v>
       </c>
       <c r="C12" t="n">
-        <v>2.1841</v>
+        <v>2.2719</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0566</v>
+        <v>1.1017</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6922</v>
+        <v>3.8406</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5732</v>
+        <v>2.3349</v>
       </c>
       <c r="G12" t="n">
-        <v>1.119</v>
+        <v>1.5113</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9069</v>
+        <v>2.3854</v>
       </c>
       <c r="I12" t="n">
-        <v>2.9818</v>
+        <v>2.3854</v>
       </c>
       <c r="J12" t="n">
-        <v>1.119</v>
+        <v>1.5113</v>
       </c>
       <c r="K12" t="n">
-        <v>201</v>
+        <v>151</v>
       </c>
       <c r="L12" t="n">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1008</v>
+        <v>3.8967</v>
       </c>
       <c r="N12" t="n">
-        <v>248</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13">
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.6707</v>
+        <v>3.7022</v>
       </c>
       <c r="C13" t="n">
-        <v>2.1713</v>
+        <v>2.19</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0468</v>
+        <v>1.0399</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6707</v>
+        <v>3.7022</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4982</v>
+        <v>3.4933</v>
       </c>
       <c r="G13" t="n">
         <v>0.1725</v>
       </c>
       <c r="H13" t="n">
-        <v>4.9315</v>
+        <v>4.9208</v>
       </c>
       <c r="I13" t="n">
-        <v>5.3226</v>
+        <v>5.3111</v>
       </c>
       <c r="J13" t="n">
         <v>0.1725</v>
@@ -1035,7 +1035,7 @@
         <v>47</v>
       </c>
       <c r="M13" t="n">
-        <v>5.495100000000001</v>
+        <v>5.4836</v>
       </c>
       <c r="N13" t="n">
         <v>288</v>
@@ -1044,185 +1044,185 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.5593</v>
+        <v>3.5528</v>
       </c>
       <c r="C14" t="n">
-        <v>2.1055</v>
+        <v>2.1016</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9961</v>
+        <v>0.9731</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5593</v>
+        <v>3.5528</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2036</v>
+        <v>3.0955</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3557</v>
+        <v>0.4069</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3761</v>
+        <v>4.0502</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2831</v>
+        <v>4.3714</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3557</v>
+        <v>0.4069</v>
       </c>
       <c r="K14" t="n">
-        <v>130</v>
+        <v>241</v>
       </c>
       <c r="L14" t="n">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6388</v>
+        <v>4.778300000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>232</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.5022</v>
+        <v>3.4388</v>
       </c>
       <c r="C15" t="n">
-        <v>2.0717</v>
+        <v>2.0342</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9701</v>
+        <v>0.9222</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5022</v>
+        <v>3.4388</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0953</v>
+        <v>2.204</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4069</v>
+        <v>1.3557</v>
       </c>
       <c r="H15" t="n">
-        <v>4.0498</v>
+        <v>2.3776</v>
       </c>
       <c r="I15" t="n">
-        <v>4.371</v>
+        <v>1.2839</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4069</v>
+        <v>1.3557</v>
       </c>
       <c r="K15" t="n">
-        <v>241</v>
+        <v>130</v>
       </c>
       <c r="L15" t="n">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="M15" t="n">
-        <v>4.777900000000001</v>
+        <v>2.6396</v>
       </c>
       <c r="N15" t="n">
-        <v>288</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.9712</v>
+        <v>3.1519</v>
       </c>
       <c r="C16" t="n">
-        <v>1.7576</v>
+        <v>1.8645</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.7941</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9712</v>
+        <v>3.1519</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3428</v>
+        <v>2.7948</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6284</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4027</v>
+        <v>3.3919</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4027</v>
+        <v>3.3919</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6284</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="L16" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.0311</v>
+        <v>3.3919</v>
       </c>
       <c r="N16" t="n">
-        <v>238</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.7948</v>
+        <v>3.1231</v>
       </c>
       <c r="C17" t="n">
-        <v>1.6532</v>
+        <v>1.8474</v>
       </c>
       <c r="D17" t="n">
-        <v>0.648</v>
+        <v>0.7812</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7948</v>
+        <v>3.1231</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7948</v>
+        <v>2.3315</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.6284</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3919</v>
+        <v>2.3781</v>
       </c>
       <c r="I17" t="n">
-        <v>3.3919</v>
+        <v>2.3781</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.6284</v>
       </c>
       <c r="K17" t="n">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3919</v>
+        <v>3.0065</v>
       </c>
       <c r="N17" t="n">
-        <v>172</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.7669</v>
+        <v>2.9511</v>
       </c>
       <c r="C18" t="n">
-        <v>1.6367</v>
+        <v>1.7457</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6353</v>
+        <v>0.7044</v>
       </c>
       <c r="E18" t="n">
-        <v>2.7669</v>
+        <v>2.9511</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8108</v>
+        <v>2.8058</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0439</v>
       </c>
       <c r="H18" t="n">
-        <v>3.4271</v>
+        <v>3.416</v>
       </c>
       <c r="I18" t="n">
-        <v>3.606</v>
+        <v>3.5943</v>
       </c>
       <c r="J18" t="n">
         <v>-0.0439</v>
@@ -1265,7 +1265,7 @@
         <v>41</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5621</v>
+        <v>3.5504</v>
       </c>
       <c r="N18" t="n">
         <v>226</v>
@@ -1278,16 +1278,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.6921</v>
+        <v>2.8532</v>
       </c>
       <c r="C19" t="n">
-        <v>1.5925</v>
+        <v>1.6878</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6012999999999999</v>
+        <v>0.6606</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6921</v>
+        <v>2.8532</v>
       </c>
       <c r="F19" t="n">
         <v>2.6921</v>
@@ -1320,231 +1320,231 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>xKacpersky</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.6191</v>
+        <v>2.7948</v>
       </c>
       <c r="C20" t="n">
-        <v>1.5493</v>
+        <v>1.6532</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5681</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6191</v>
+        <v>2.7948</v>
       </c>
       <c r="F20" t="n">
-        <v>2.6191</v>
+        <v>2.5187</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3.0074</v>
+        <v>2.7878</v>
       </c>
       <c r="I20" t="n">
-        <v>3.0074</v>
+        <v>2.7878</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.0074</v>
+        <v>2.7878</v>
       </c>
       <c r="N20" t="n">
-        <v>138</v>
+        <v>166</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>xKacpersky</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.5789</v>
+        <v>2.7016</v>
       </c>
       <c r="C21" t="n">
-        <v>1.5255</v>
+        <v>1.5981</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5498</v>
+        <v>0.5929</v>
       </c>
       <c r="E21" t="n">
-        <v>2.5789</v>
+        <v>2.7016</v>
       </c>
       <c r="F21" t="n">
-        <v>2.8297</v>
+        <v>2.6194</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2508</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.4684</v>
+        <v>3.0082</v>
       </c>
       <c r="I21" t="n">
-        <v>3.4684</v>
+        <v>3.0082</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2508</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="L21" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2176</v>
+        <v>3.0082</v>
       </c>
       <c r="N21" t="n">
-        <v>263</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.5188</v>
+        <v>2.6545</v>
       </c>
       <c r="C22" t="n">
-        <v>1.49</v>
+        <v>1.5702</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5224</v>
+        <v>0.5719</v>
       </c>
       <c r="E22" t="n">
-        <v>2.5188</v>
+        <v>2.6545</v>
       </c>
       <c r="F22" t="n">
-        <v>2.5188</v>
+        <v>2.3343</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.7879</v>
+        <v>2.3841</v>
       </c>
       <c r="I22" t="n">
-        <v>2.7879</v>
+        <v>2.3841</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.7879</v>
+        <v>2.3841</v>
       </c>
       <c r="N22" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.4888</v>
+        <v>2.6186</v>
       </c>
       <c r="C23" t="n">
-        <v>1.4722</v>
+        <v>1.549</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5087</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>2.4888</v>
+        <v>2.6186</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1458</v>
+        <v>2.8297</v>
       </c>
       <c r="G23" t="n">
-        <v>0.343</v>
+        <v>-0.2504</v>
       </c>
       <c r="H23" t="n">
-        <v>2.1458</v>
+        <v>3.4684</v>
       </c>
       <c r="I23" t="n">
-        <v>2.2578</v>
+        <v>3.4684</v>
       </c>
       <c r="J23" t="n">
-        <v>0.343</v>
+        <v>-0.2504</v>
       </c>
       <c r="K23" t="n">
-        <v>185</v>
+        <v>151</v>
       </c>
       <c r="L23" t="n">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="M23" t="n">
-        <v>2.6008</v>
+        <v>3.218</v>
       </c>
       <c r="N23" t="n">
-        <v>226</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.3345</v>
+        <v>2.5426</v>
       </c>
       <c r="C24" t="n">
-        <v>1.3809</v>
+        <v>1.504</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4385</v>
+        <v>0.5219</v>
       </c>
       <c r="E24" t="n">
-        <v>2.3345</v>
+        <v>2.5426</v>
       </c>
       <c r="F24" t="n">
-        <v>2.3345</v>
+        <v>2.1465</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.343</v>
       </c>
       <c r="H24" t="n">
-        <v>2.3845</v>
+        <v>2.1465</v>
       </c>
       <c r="I24" t="n">
-        <v>2.3845</v>
+        <v>2.2586</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.343</v>
       </c>
       <c r="K24" t="n">
-        <v>139</v>
+        <v>185</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M24" t="n">
-        <v>2.3845</v>
+        <v>2.6016</v>
       </c>
       <c r="N24" t="n">
-        <v>139</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.1397</v>
+        <v>2.1323</v>
       </c>
       <c r="C25" t="n">
-        <v>1.2657</v>
+        <v>1.2613</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3498</v>
+        <v>0.3386</v>
       </c>
       <c r="E25" t="n">
-        <v>2.1397</v>
+        <v>2.1323</v>
       </c>
       <c r="F25" t="n">
-        <v>2.8014</v>
+        <v>2.81</v>
       </c>
       <c r="G25" t="n">
         <v>-0.6617</v>
       </c>
       <c r="H25" t="n">
-        <v>3.4064</v>
+        <v>3.4253</v>
       </c>
       <c r="I25" t="n">
-        <v>3.6766</v>
+        <v>3.697</v>
       </c>
       <c r="J25" t="n">
         <v>-0.6617</v>
@@ -1587,7 +1587,7 @@
         <v>47</v>
       </c>
       <c r="M25" t="n">
-        <v>3.0149</v>
+        <v>3.0353</v>
       </c>
       <c r="N25" t="n">
         <v>288</v>
@@ -1596,124 +1596,124 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>xiELO</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.1069</v>
+        <v>2.0024</v>
       </c>
       <c r="C26" t="n">
-        <v>1.2463</v>
+        <v>1.1845</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3349</v>
+        <v>0.2806</v>
       </c>
       <c r="E26" t="n">
-        <v>2.1069</v>
+        <v>2.0024</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1418</v>
+        <v>1.9192</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9651</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.1418</v>
+        <v>1.9192</v>
       </c>
       <c r="I26" t="n">
-        <v>1.1418</v>
+        <v>1.9192</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9651</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="L26" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.1069</v>
+        <v>1.9192</v>
       </c>
       <c r="N26" t="n">
-        <v>263</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>xiELO</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.9296</v>
+        <v>1.951</v>
       </c>
       <c r="C27" t="n">
-        <v>1.1414</v>
+        <v>1.1541</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2542</v>
+        <v>0.2576</v>
       </c>
       <c r="E27" t="n">
-        <v>1.9296</v>
+        <v>1.951</v>
       </c>
       <c r="F27" t="n">
-        <v>1.9296</v>
+        <v>1.1418</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.9655</v>
       </c>
       <c r="H27" t="n">
-        <v>1.9296</v>
+        <v>1.1418</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9296</v>
+        <v>1.1418</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.9655</v>
       </c>
       <c r="K27" t="n">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="M27" t="n">
-        <v>1.9296</v>
+        <v>2.1073</v>
       </c>
       <c r="N27" t="n">
-        <v>173</v>
+        <v>263</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HUASOPEEK</t>
+          <t>luchov</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.7301</v>
+        <v>1.875</v>
       </c>
       <c r="C28" t="n">
-        <v>1.0234</v>
+        <v>1.1091</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1634</v>
+        <v>0.2237</v>
       </c>
       <c r="E28" t="n">
-        <v>1.7301</v>
+        <v>1.875</v>
       </c>
       <c r="F28" t="n">
-        <v>1.7301</v>
+        <v>1.6474</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.7301</v>
+        <v>1.6474</v>
       </c>
       <c r="I28" t="n">
-        <v>1.7301</v>
+        <v>1.6474</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.7301</v>
+        <v>1.6474</v>
       </c>
       <c r="N28" t="n">
         <v>139</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cobrazera</t>
+          <t>HUASOPEEK</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.7142</v>
+        <v>1.8659</v>
       </c>
       <c r="C29" t="n">
-        <v>1.014</v>
+        <v>1.1037</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1561</v>
+        <v>0.2196</v>
       </c>
       <c r="E29" t="n">
-        <v>1.7142</v>
+        <v>1.8659</v>
       </c>
       <c r="F29" t="n">
-        <v>2.6275</v>
+        <v>1.7474</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.9133</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>3.0257</v>
+        <v>1.7474</v>
       </c>
       <c r="I29" t="n">
-        <v>3.1837</v>
+        <v>1.7474</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.9133</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="L29" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.2704</v>
+        <v>1.7474</v>
       </c>
       <c r="N29" t="n">
-        <v>226</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>luchov</t>
+          <t>cobrazera</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.6477</v>
+        <v>1.6983</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9747</v>
+        <v>1.0046</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1259</v>
+        <v>0.1448</v>
       </c>
       <c r="E30" t="n">
-        <v>1.6477</v>
+        <v>1.6983</v>
       </c>
       <c r="F30" t="n">
-        <v>1.6477</v>
+        <v>2.62</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.9133</v>
       </c>
       <c r="H30" t="n">
-        <v>1.6477</v>
+        <v>3.0095</v>
       </c>
       <c r="I30" t="n">
-        <v>1.6477</v>
+        <v>3.1666</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.9133</v>
       </c>
       <c r="K30" t="n">
-        <v>139</v>
+        <v>185</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M30" t="n">
-        <v>1.6477</v>
+        <v>2.2533</v>
       </c>
       <c r="N30" t="n">
-        <v>139</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31">
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.6</v>
+        <v>1.6262</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9465</v>
+        <v>0.962</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1041</v>
+        <v>0.1126</v>
       </c>
       <c r="E31" t="n">
-        <v>1.6</v>
+        <v>1.6262</v>
       </c>
       <c r="F31" t="n">
         <v>1.2598</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3402</v>
+        <v>0.3405</v>
       </c>
       <c r="H31" t="n">
         <v>1.2598</v>
@@ -1854,7 +1854,7 @@
         <v>1.2598</v>
       </c>
       <c r="J31" t="n">
-        <v>0.3402</v>
+        <v>0.3405</v>
       </c>
       <c r="K31" t="n">
         <v>151</v>
@@ -1863,7 +1863,7 @@
         <v>112</v>
       </c>
       <c r="M31" t="n">
-        <v>1.6</v>
+        <v>1.6003</v>
       </c>
       <c r="N31" t="n">
         <v>263</v>
@@ -1872,369 +1872,369 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>r1nkle</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.5631</v>
+        <v>1.4378</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9246</v>
+        <v>0.8505</v>
       </c>
       <c r="D32" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0284</v>
       </c>
       <c r="E32" t="n">
-        <v>1.5631</v>
+        <v>1.4378</v>
       </c>
       <c r="F32" t="n">
-        <v>2.1451</v>
+        <v>1.1638</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.582</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.1832</v>
+        <v>1.1638</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1789</v>
+        <v>1.1638</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.582</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="L32" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.5969000000000001</v>
+        <v>1.1638</v>
       </c>
       <c r="N32" t="n">
-        <v>232</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.4807</v>
+        <v>1.3796</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8759</v>
+        <v>0.8161</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0498</v>
+        <v>0.0024</v>
       </c>
       <c r="E33" t="n">
-        <v>1.4807</v>
+        <v>1.3796</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7562</v>
+        <v>1.4702</v>
       </c>
       <c r="G33" t="n">
-        <v>0.7245</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7562</v>
+        <v>1.4702</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7562</v>
+        <v>1.5081</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7245</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>161</v>
+        <v>228</v>
       </c>
       <c r="L33" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.4807</v>
+        <v>1.5081</v>
       </c>
       <c r="N33" t="n">
-        <v>238</v>
+        <v>228</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.4702</v>
+        <v>1.3028</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8697</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0451</v>
+        <v>-0.0319</v>
       </c>
       <c r="E34" t="n">
-        <v>1.4702</v>
+        <v>1.3028</v>
       </c>
       <c r="F34" t="n">
-        <v>1.4702</v>
+        <v>0.7565</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.7245</v>
       </c>
       <c r="H34" t="n">
-        <v>1.4702</v>
+        <v>0.7565</v>
       </c>
       <c r="I34" t="n">
-        <v>1.5081</v>
+        <v>0.7565</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.7245</v>
       </c>
       <c r="K34" t="n">
-        <v>228</v>
+        <v>161</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M34" t="n">
-        <v>1.5081</v>
+        <v>1.481</v>
       </c>
       <c r="N34" t="n">
-        <v>228</v>
+        <v>238</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.3542</v>
+        <v>1.2416</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8011</v>
+        <v>0.7345</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0077</v>
+        <v>-0.0592</v>
       </c>
       <c r="E35" t="n">
-        <v>1.3542</v>
+        <v>1.2416</v>
       </c>
       <c r="F35" t="n">
-        <v>1.3542</v>
+        <v>2.0741</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.582</v>
       </c>
       <c r="H35" t="n">
-        <v>1.3542</v>
+        <v>2.0741</v>
       </c>
       <c r="I35" t="n">
-        <v>1.3542</v>
+        <v>1.12</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.582</v>
       </c>
       <c r="K35" t="n">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M35" t="n">
-        <v>1.3542</v>
+        <v>0.5380000000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>139</v>
+        <v>232</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.2712</v>
+        <v>1.227</v>
       </c>
       <c r="C36" t="n">
-        <v>0.752</v>
+        <v>0.7258</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0455</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>1.2712</v>
+        <v>1.227</v>
       </c>
       <c r="F36" t="n">
-        <v>1.2712</v>
+        <v>0.5879</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>1.2712</v>
+        <v>0.5879</v>
       </c>
       <c r="I36" t="n">
-        <v>1.2712</v>
+        <v>0.5879</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M36" t="n">
-        <v>1.2712</v>
+        <v>1.165</v>
       </c>
       <c r="N36" t="n">
-        <v>139</v>
+        <v>238</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.1645</v>
+        <v>1.2026</v>
       </c>
       <c r="C37" t="n">
-        <v>0.6888</v>
+        <v>0.7114</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0941</v>
+        <v>-0.0766</v>
       </c>
       <c r="E37" t="n">
-        <v>1.1645</v>
+        <v>1.2026</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5874</v>
+        <v>1.3875</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5770999999999999</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5874</v>
+        <v>1.3875</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5874</v>
+        <v>1.3875</v>
       </c>
       <c r="J37" t="n">
-        <v>0.5770999999999999</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="L37" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.1645</v>
+        <v>1.3875</v>
       </c>
       <c r="N37" t="n">
-        <v>238</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>r1nkle</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.1637</v>
+        <v>1.1448</v>
       </c>
       <c r="C38" t="n">
-        <v>0.6884</v>
+        <v>0.6772</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0945</v>
+        <v>-0.1025</v>
       </c>
       <c r="E38" t="n">
-        <v>1.1637</v>
+        <v>1.1448</v>
       </c>
       <c r="F38" t="n">
-        <v>1.1637</v>
+        <v>1.2708</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.1637</v>
+        <v>1.2708</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1637</v>
+        <v>1.2708</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.1637</v>
+        <v>1.2708</v>
       </c>
       <c r="N38" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>NucleonZ</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.1355</v>
+        <v>1.1283</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6717</v>
+        <v>0.6674</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1073</v>
+        <v>-0.1098</v>
       </c>
       <c r="E39" t="n">
-        <v>1.1355</v>
+        <v>1.1283</v>
       </c>
       <c r="F39" t="n">
-        <v>1.1355</v>
+        <v>0.9253</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.1355</v>
+        <v>0.9253</v>
       </c>
       <c r="I39" t="n">
-        <v>1.1355</v>
+        <v>0.9253</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>166</v>
+        <v>40</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.1355</v>
+        <v>0.9253</v>
       </c>
       <c r="N39" t="n">
-        <v>166</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40">
@@ -2244,16 +2244,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.0272</v>
+        <v>0.9872</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6076</v>
+        <v>0.584</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1566</v>
+        <v>-0.1729</v>
       </c>
       <c r="E40" t="n">
-        <v>1.0272</v>
+        <v>0.9872</v>
       </c>
       <c r="F40" t="n">
         <v>1.0272</v>
@@ -2286,400 +2286,400 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9528</v>
+        <v>0.9721</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5636</v>
+        <v>0.575</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1905</v>
+        <v>-0.1796</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9528</v>
+        <v>0.9721</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9528</v>
+        <v>1.3515</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-0.4299</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9528</v>
+        <v>1.3515</v>
       </c>
       <c r="I41" t="n">
-        <v>0.9528</v>
+        <v>1.4221</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-0.4299</v>
       </c>
       <c r="K41" t="n">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M41" t="n">
-        <v>0.9528</v>
+        <v>0.9922</v>
       </c>
       <c r="N41" t="n">
-        <v>172</v>
+        <v>226</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NucleonZ</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9256</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5475</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2029</v>
+        <v>-0.1849</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9256</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9256</v>
+        <v>1.1354</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9256</v>
+        <v>1.1354</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9256</v>
+        <v>1.1354</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>40</v>
+        <v>166</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.9256</v>
+        <v>1.1354</v>
       </c>
       <c r="N42" t="n">
-        <v>40</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9213</v>
+        <v>0.9448</v>
       </c>
       <c r="C43" t="n">
-        <v>0.545</v>
+        <v>0.5589</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2048</v>
+        <v>-0.1918</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9213</v>
+        <v>0.9448</v>
       </c>
       <c r="F43" t="n">
-        <v>1.3512</v>
+        <v>0.9528</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.4299</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.3512</v>
+        <v>0.9528</v>
       </c>
       <c r="I43" t="n">
-        <v>1.4217</v>
+        <v>0.9528</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.4299</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="L43" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.9918</v>
+        <v>0.9528</v>
       </c>
       <c r="N43" t="n">
-        <v>226</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8966</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5304</v>
+        <v>0.4809</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2161</v>
+        <v>-0.2507</v>
       </c>
       <c r="E44" t="n">
-        <v>0.8966</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8966</v>
+        <v>0.7419</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8966</v>
+        <v>0.7419</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8966</v>
+        <v>0.7419</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.8966</v>
+        <v>0.7419</v>
       </c>
       <c r="N44" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>cairne</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.8128</v>
       </c>
       <c r="C45" t="n">
-        <v>0.5006</v>
+        <v>0.4808</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.239</v>
+        <v>-0.2508</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.8128</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.7632</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.7632</v>
       </c>
       <c r="I45" t="n">
-        <v>0.8681</v>
+        <v>0.7632</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>228</v>
+        <v>138</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.8681</v>
+        <v>0.7632</v>
       </c>
       <c r="N45" t="n">
-        <v>228</v>
+        <v>138</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cairne</t>
+          <t>esenthial</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7631</v>
+        <v>0.8117</v>
       </c>
       <c r="C46" t="n">
-        <v>0.4514</v>
+        <v>0.4801</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2768</v>
+        <v>-0.2513</v>
       </c>
       <c r="E46" t="n">
-        <v>0.7631</v>
+        <v>0.8117</v>
       </c>
       <c r="F46" t="n">
-        <v>0.7631</v>
+        <v>0.7399</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.7631</v>
+        <v>0.7399</v>
       </c>
       <c r="I46" t="n">
-        <v>0.7631</v>
+        <v>0.7399</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.7631</v>
+        <v>0.7399</v>
       </c>
       <c r="N46" t="n">
-        <v>138</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7419</v>
+        <v>0.8072</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4389</v>
+        <v>0.4775</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2865</v>
+        <v>-0.2533</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7419</v>
+        <v>0.8072</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7419</v>
+        <v>0.8959</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.7419</v>
+        <v>0.8959</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7419</v>
+        <v>0.8959</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.7419</v>
+        <v>0.8959</v>
       </c>
       <c r="N47" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>npl</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7416</v>
+        <v>0.7842</v>
       </c>
       <c r="C48" t="n">
-        <v>0.4387</v>
+        <v>0.4639</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2866</v>
+        <v>-0.2635</v>
       </c>
       <c r="E48" t="n">
-        <v>0.7416</v>
+        <v>0.7842</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7416</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.7416</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7416</v>
+        <v>0.8681</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>119</v>
+        <v>228</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.7416</v>
+        <v>0.8681</v>
       </c>
       <c r="N48" t="n">
-        <v>119</v>
+        <v>228</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>esenthial</t>
+          <t>npl</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.7794</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4326</v>
+        <v>0.461</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2913</v>
+        <v>-0.2657</v>
       </c>
       <c r="E49" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.7794</v>
       </c>
       <c r="F49" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.7553</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.7553</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.7553</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.7553</v>
       </c>
       <c r="N49" t="n">
         <v>119</v>
@@ -2700,47 +2700,47 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7292</v>
+        <v>0.7241</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4313</v>
+        <v>0.4283</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2923</v>
+        <v>-0.2904</v>
       </c>
       <c r="E50" t="n">
-        <v>0.7292</v>
+        <v>0.7241</v>
       </c>
       <c r="F50" t="n">
-        <v>1.4505</v>
+        <v>0.5982</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.7213000000000001</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1.4505</v>
+        <v>0.5982</v>
       </c>
       <c r="I50" t="n">
-        <v>1.4505</v>
+        <v>0.5982</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.7213000000000001</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="L50" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.7291999999999998</v>
+        <v>0.5982</v>
       </c>
       <c r="N50" t="n">
-        <v>263</v>
+        <v>137</v>
       </c>
     </row>
     <row r="51">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6703</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="C51" t="n">
-        <v>0.3965</v>
+        <v>0.401</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3191</v>
+        <v>-0.311</v>
       </c>
       <c r="E51" t="n">
-        <v>0.6703</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.5765</v>
+        <v>-0.5845</v>
       </c>
       <c r="G51" t="n">
         <v>1.2468</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.5765</v>
+        <v>-0.5845</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3113</v>
+        <v>-0.3156</v>
       </c>
       <c r="J51" t="n">
         <v>1.2468</v>
@@ -2783,7 +2783,7 @@
         <v>131</v>
       </c>
       <c r="M51" t="n">
-        <v>0.9354999999999999</v>
+        <v>0.9311999999999999</v>
       </c>
       <c r="N51" t="n">
         <v>319</v>
@@ -2792,737 +2792,737 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>nota</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5982</v>
+        <v>0.6197</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3539</v>
+        <v>0.3666</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3519</v>
+        <v>-0.337</v>
       </c>
       <c r="E52" t="n">
-        <v>0.5982</v>
+        <v>0.6197</v>
       </c>
       <c r="F52" t="n">
-        <v>0.5982</v>
+        <v>1.4505</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-0.7209</v>
       </c>
       <c r="H52" t="n">
-        <v>0.5982</v>
+        <v>1.4505</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5982</v>
+        <v>1.4505</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-0.7209</v>
       </c>
       <c r="K52" t="n">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="M52" t="n">
-        <v>0.5982</v>
+        <v>0.7295999999999999</v>
       </c>
       <c r="N52" t="n">
-        <v>137</v>
+        <v>263</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4821</v>
+        <v>0.4646</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2852</v>
+        <v>0.2748</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4047</v>
+        <v>-0.4063</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4821</v>
+        <v>0.4646</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4821</v>
+        <v>0.4256</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.4821</v>
+        <v>0.4256</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4821</v>
+        <v>0.4256</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.4821</v>
+        <v>0.4256</v>
       </c>
       <c r="N53" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4253</v>
+        <v>0.4023</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2516</v>
+        <v>0.238</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4306</v>
+        <v>-0.4341</v>
       </c>
       <c r="E54" t="n">
-        <v>0.4253</v>
+        <v>0.4023</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4253</v>
+        <v>0.407</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.4253</v>
+        <v>0.407</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4253</v>
+        <v>0.407</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.4253</v>
+        <v>0.407</v>
       </c>
       <c r="N54" t="n">
-        <v>173</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.407</v>
+        <v>0.3354</v>
       </c>
       <c r="C55" t="n">
-        <v>0.2408</v>
+        <v>0.1984</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4389</v>
+        <v>-0.464</v>
       </c>
       <c r="E55" t="n">
-        <v>0.407</v>
+        <v>0.3354</v>
       </c>
       <c r="F55" t="n">
-        <v>0.407</v>
+        <v>0.4821</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.407</v>
+        <v>0.4821</v>
       </c>
       <c r="I55" t="n">
-        <v>0.407</v>
+        <v>0.4821</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.407</v>
+        <v>0.4821</v>
       </c>
       <c r="N55" t="n">
-        <v>137</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.3805</v>
+        <v>0.3137</v>
       </c>
       <c r="C56" t="n">
-        <v>0.2251</v>
+        <v>0.1856</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.451</v>
+        <v>-0.4737</v>
       </c>
       <c r="E56" t="n">
-        <v>0.3805</v>
+        <v>0.3137</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3805</v>
+        <v>0.2686</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3805</v>
+        <v>0.2686</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3805</v>
+        <v>0.2686</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.3805</v>
+        <v>0.2686</v>
       </c>
       <c r="N56" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.3683</v>
+        <v>0.2893</v>
       </c>
       <c r="C57" t="n">
-        <v>0.2179</v>
+        <v>0.1711</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4565</v>
+        <v>-0.4846</v>
       </c>
       <c r="E57" t="n">
-        <v>0.3683</v>
+        <v>0.2893</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7095</v>
+        <v>0.2448</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.3412</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.7095</v>
+        <v>0.2448</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7658</v>
+        <v>0.2448</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.3412</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>241</v>
+        <v>139</v>
       </c>
       <c r="L57" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.4246</v>
+        <v>0.2448</v>
       </c>
       <c r="N57" t="n">
-        <v>288</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>meyern</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.3137</v>
+        <v>0.2671</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1856</v>
+        <v>0.158</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4814</v>
+        <v>-0.4945</v>
       </c>
       <c r="E58" t="n">
-        <v>0.3137</v>
+        <v>0.2671</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3137</v>
+        <v>0.2024</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.3137</v>
+        <v>0.2024</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3137</v>
+        <v>0.2024</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.3137</v>
+        <v>0.2024</v>
       </c>
       <c r="N58" t="n">
-        <v>139</v>
+        <v>107</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>meyern</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.2686</v>
+        <v>0.2274</v>
       </c>
       <c r="C59" t="n">
-        <v>0.1589</v>
+        <v>0.1345</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5019</v>
+        <v>-0.5122</v>
       </c>
       <c r="E59" t="n">
-        <v>0.2686</v>
+        <v>0.2274</v>
       </c>
       <c r="F59" t="n">
-        <v>0.2686</v>
+        <v>0.3133</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2686</v>
+        <v>0.3133</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2686</v>
+        <v>0.3133</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.2686</v>
+        <v>0.3133</v>
       </c>
       <c r="N59" t="n">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.2455</v>
+        <v>0.2201</v>
       </c>
       <c r="C60" t="n">
-        <v>0.1452</v>
+        <v>0.1302</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5124</v>
+        <v>-0.5155</v>
       </c>
       <c r="E60" t="n">
-        <v>0.2455</v>
+        <v>0.2201</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2455</v>
+        <v>0.3805</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.2455</v>
+        <v>0.3805</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2455</v>
+        <v>0.3805</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0.2455</v>
+        <v>0.3805</v>
       </c>
       <c r="N60" t="n">
-        <v>139</v>
+        <v>172</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.2026</v>
+        <v>0.1635</v>
       </c>
       <c r="C61" t="n">
-        <v>0.1198</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.532</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>0.2026</v>
+        <v>0.1635</v>
       </c>
       <c r="F61" t="n">
-        <v>0.2026</v>
+        <v>0.7093</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>-0.3412</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2026</v>
+        <v>0.7093</v>
       </c>
       <c r="I61" t="n">
-        <v>0.2026</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>-0.3412</v>
       </c>
       <c r="K61" t="n">
-        <v>107</v>
+        <v>241</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M61" t="n">
-        <v>0.2026</v>
+        <v>0.4243999999999999</v>
       </c>
       <c r="N61" t="n">
-        <v>107</v>
+        <v>288</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.0613</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0363</v>
+        <v>0.0471</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5963000000000001</v>
+        <v>-0.5782</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0613</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0613</v>
+        <v>0.0139</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0613</v>
+        <v>0.0139</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0613</v>
+        <v>0.0139</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0.0613</v>
+        <v>0.0139</v>
       </c>
       <c r="N62" t="n">
-        <v>137</v>
+        <v>107</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.002</v>
+        <v>-0.0658</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0012</v>
+        <v>-0.0389</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6233</v>
+        <v>-0.6432</v>
       </c>
       <c r="E63" t="n">
-        <v>0.002</v>
+        <v>-0.0658</v>
       </c>
       <c r="F63" t="n">
-        <v>0.002</v>
+        <v>-0.0083</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.002</v>
+        <v>-0.0083</v>
       </c>
       <c r="I63" t="n">
-        <v>0.002</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>107</v>
+        <v>228</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0.002</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="N63" t="n">
-        <v>107</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.0083</v>
+        <v>-0.0725</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.0049</v>
+        <v>-0.0429</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.628</v>
+        <v>-0.6462</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.0083</v>
+        <v>-0.0725</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.0083</v>
+        <v>0.0613</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.0083</v>
+        <v>0.0613</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>228</v>
+        <v>137</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="N64" t="n">
-        <v>228</v>
+        <v>137</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.1827</v>
+        <v>-0.2116</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.1081</v>
+        <v>-0.1252</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7074</v>
+        <v>-0.7083</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.1827</v>
+        <v>-0.2116</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.1827</v>
+        <v>-0.2557</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.1827</v>
+        <v>-0.2557</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1827</v>
+        <v>-0.2557</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.1827</v>
+        <v>-0.2557</v>
       </c>
       <c r="N65" t="n">
-        <v>173</v>
+        <v>138</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>soulfly</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.1853</v>
+        <v>-0.2326</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1096</v>
+        <v>-0.1376</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7086</v>
+        <v>-0.7177</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.1853</v>
+        <v>-0.2326</v>
       </c>
       <c r="F66" t="n">
-        <v>1.4162</v>
+        <v>-0.1826</v>
       </c>
       <c r="G66" t="n">
-        <v>-1.6015</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>1.4162</v>
+        <v>-0.1826</v>
       </c>
       <c r="I66" t="n">
-        <v>1.4162</v>
+        <v>-0.1826</v>
       </c>
       <c r="J66" t="n">
-        <v>-1.6015</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="L66" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.1853</v>
+        <v>-0.1826</v>
       </c>
       <c r="N66" t="n">
-        <v>238</v>
+        <v>173</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>soulfly</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.2445</v>
+        <v>-0.3528</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.1446</v>
+        <v>-0.2087</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7355</v>
+        <v>-0.7714</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.2445</v>
+        <v>-0.3528</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.2445</v>
+        <v>1.4166</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>-1.6015</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.2445</v>
+        <v>1.4166</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.2445</v>
+        <v>1.4166</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>-1.6015</v>
       </c>
       <c r="K67" t="n">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.2445</v>
+        <v>-0.1848999999999998</v>
       </c>
       <c r="N67" t="n">
-        <v>138</v>
+        <v>238</v>
       </c>
     </row>
     <row r="68">
@@ -3532,16 +3532,16 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.3725</v>
+        <v>-0.4652</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2203</v>
+        <v>-0.2752</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7938</v>
+        <v>-0.8216</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.3725</v>
+        <v>-0.4652</v>
       </c>
       <c r="F68" t="n">
         <v>-0.3725</v>
@@ -3578,28 +3578,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.4966</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.2938</v>
+        <v>-0.3456</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-0.8748</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.4966</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.4966</v>
+        <v>-0.4965</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.4966</v>
+        <v>-0.4965</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4966</v>
+        <v>-0.4965</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.4966</v>
+        <v>-0.4965</v>
       </c>
       <c r="N69" t="n">
         <v>138</v>
@@ -3620,47 +3620,47 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>kensizor</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.6486</v>
+        <v>-0.6197</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.3837</v>
+        <v>-0.3666</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9195</v>
+        <v>-0.8905999999999999</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.6486</v>
+        <v>-0.6197</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.0514</v>
+        <v>-0.6833</v>
       </c>
       <c r="G70" t="n">
-        <v>0.4028</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.0514</v>
+        <v>-0.6833</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.1063</v>
+        <v>-0.6833</v>
       </c>
       <c r="J70" t="n">
-        <v>0.4028</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>185</v>
+        <v>119</v>
       </c>
       <c r="L70" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.7035</v>
+        <v>-0.6833</v>
       </c>
       <c r="N70" t="n">
-        <v>226</v>
+        <v>119</v>
       </c>
     </row>
     <row r="71">
@@ -3670,28 +3670,28 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.6851</v>
+        <v>-0.8173</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.4053</v>
+        <v>-0.4835</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9361</v>
+        <v>-0.9789</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.6851</v>
+        <v>-0.8173</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.6851</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.6851</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6851</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.6851</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="N71" t="n">
         <v>119</v>
@@ -3712,93 +3712,93 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.7224</v>
+        <v>-0.8202</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.4273</v>
+        <v>-0.4852</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9530999999999999</v>
+        <v>-0.9802</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.7224</v>
+        <v>-0.8202</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.7224</v>
+        <v>-1.0507</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>0.4028</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.7224</v>
+        <v>-1.0507</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.7224</v>
+        <v>-1.1055</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>0.4028</v>
       </c>
       <c r="K72" t="n">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.7224</v>
+        <v>-0.7026999999999999</v>
       </c>
       <c r="N72" t="n">
-        <v>172</v>
+        <v>226</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kensizor</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.7345</v>
+        <v>-0.9196</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.4345</v>
+        <v>-0.544</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9586</v>
+        <v>-1.0246</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.7345</v>
+        <v>-0.9196</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.7345</v>
+        <v>-0.7224</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.7345</v>
+        <v>-0.7224</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.7345</v>
+        <v>-0.7224</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.7345</v>
+        <v>-0.7224</v>
       </c>
       <c r="N73" t="n">
-        <v>119</v>
+        <v>172</v>
       </c>
     </row>
     <row r="74">
@@ -3808,28 +3808,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.7906</v>
+        <v>-0.9709</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.4677</v>
+        <v>-0.5743</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9841</v>
+        <v>-1.0475</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.7906</v>
+        <v>-0.9709</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.7906</v>
+        <v>-0.7782</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.7906</v>
+        <v>-0.7782</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.7906</v>
+        <v>-0.7782</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.7906</v>
+        <v>-0.7782</v>
       </c>
       <c r="N74" t="n">
         <v>166</v>
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.9041</v>
+        <v>-1.0107</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.5979</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0358</v>
+        <v>-1.0653</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.9041</v>
+        <v>-1.0107</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.9041</v>
+        <v>-0.9039</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.9041</v>
+        <v>-0.9039</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.9041</v>
+        <v>-0.9039</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.9041</v>
+        <v>-0.9039</v>
       </c>
       <c r="N75" t="n">
         <v>107</v>
@@ -3900,28 +3900,28 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.0322</v>
+        <v>-1.3669</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.6106</v>
+        <v>-0.8086</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0941</v>
+        <v>-1.2244</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.0322</v>
+        <v>-1.3669</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.0322</v>
+        <v>-1.042</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.0322</v>
+        <v>-1.042</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.0322</v>
+        <v>-1.042</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.0322</v>
+        <v>-1.042</v>
       </c>
       <c r="N76" t="n">
         <v>107</v>
@@ -3946,28 +3946,28 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.093</v>
+        <v>-1.3787</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.6465</v>
+        <v>-0.8156</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1218</v>
+        <v>-1.2297</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.093</v>
+        <v>-1.3787</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.093</v>
+        <v>-1.0939</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.093</v>
+        <v>-1.0939</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.093</v>
+        <v>-1.0939</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.093</v>
+        <v>-1.0939</v>
       </c>
       <c r="N77" t="n">
         <v>119</v>
@@ -3992,28 +3992,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.6754</v>
+        <v>-1.989</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.9911</v>
+        <v>-1.1766</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3869</v>
+        <v>-1.5023</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.6754</v>
+        <v>-1.989</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.6754</v>
+        <v>-1.6757</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.6754</v>
+        <v>-1.6757</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.6754</v>
+        <v>-1.6757</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.6754</v>
+        <v>-1.6757</v>
       </c>
       <c r="N78" t="n">
         <v>139</v>
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.7829</v>
+        <v>-2.0859</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.0546</v>
+        <v>-1.2339</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.4358</v>
+        <v>-1.5455</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.7829</v>
+        <v>-2.0859</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.0556</v>
+        <v>-2.053</v>
       </c>
       <c r="G79" t="n">
         <v>0.2727</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.0556</v>
+        <v>-2.053</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.11</v>
+        <v>-1.1086</v>
       </c>
       <c r="J79" t="n">
         <v>0.2727</v>
@@ -4071,7 +4071,7 @@
         <v>131</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.8373000000000002</v>
+        <v>-0.8359000000000001</v>
       </c>
       <c r="N79" t="n">
         <v>319</v>
@@ -4084,28 +4084,28 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.8496</v>
+        <v>-2.1862</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.0941</v>
+        <v>-1.2932</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.4662</v>
+        <v>-1.5903</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.8496</v>
+        <v>-2.1862</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.8496</v>
+        <v>-1.8495</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.8496</v>
+        <v>-1.8495</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.8496</v>
+        <v>-1.8495</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.8496</v>
+        <v>-1.8495</v>
       </c>
       <c r="N80" t="n">
         <v>173</v>
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.5714</v>
+        <v>-3.0422</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.5211</v>
+        <v>-1.7996</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.7948</v>
+        <v>-1.9727</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.5714</v>
+        <v>-3.0422</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.5714</v>
+        <v>-2.5621</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.5714</v>
+        <v>-2.5621</v>
       </c>
       <c r="I81" t="n">
-        <v>-2.5714</v>
+        <v>-2.5621</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-2.5714</v>
+        <v>-2.5621</v>
       </c>
       <c r="N81" t="n">
         <v>139</v>
@@ -4176,28 +4176,28 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-2.9307</v>
+        <v>-3.2769</v>
       </c>
       <c r="C82" t="n">
-        <v>-1.7336</v>
+        <v>-1.9384</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.9583</v>
+        <v>-2.0775</v>
       </c>
       <c r="E82" t="n">
-        <v>-2.9307</v>
+        <v>-3.2769</v>
       </c>
       <c r="F82" t="n">
-        <v>-2.9307</v>
+        <v>-2.9309</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-2.9307</v>
+        <v>-2.9309</v>
       </c>
       <c r="I82" t="n">
-        <v>-2.9307</v>
+        <v>-2.9309</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -4209,7 +4209,7 @@
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>-2.9307</v>
+        <v>-2.9309</v>
       </c>
       <c r="N82" t="n">
         <v>166</v>
@@ -7915,10 +7915,10 @@
         <v>1.37</v>
       </c>
       <c r="I92" t="n">
-        <v>0.7955</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="J92" t="n">
-        <v>18.2965</v>
+        <v>18.3057</v>
       </c>
     </row>
     <row r="93">
@@ -7952,13 +7952,13 @@
         <v>23</v>
       </c>
       <c r="H93" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="I93" t="n">
-        <v>0.7202</v>
+        <v>0.7054</v>
       </c>
       <c r="J93" t="n">
-        <v>16.5646</v>
+        <v>16.2242</v>
       </c>
     </row>
     <row r="94">
@@ -7995,10 +7995,10 @@
         <v>1.21</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5465</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="J94" t="n">
-        <v>12.5695</v>
+        <v>12.5787</v>
       </c>
     </row>
     <row r="95">
@@ -8035,10 +8035,10 @@
         <v>0.93</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2776</v>
+        <v>-0.2772</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.3848</v>
+        <v>-6.3756</v>
       </c>
     </row>
     <row r="96">
@@ -8075,10 +8075,10 @@
         <v>0.64</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.9526</v>
+        <v>-0.9523</v>
       </c>
       <c r="J96" t="n">
-        <v>-21.9098</v>
+        <v>-21.9029</v>
       </c>
     </row>
     <row r="97">
@@ -9512,13 +9512,13 @@
         <v>22</v>
       </c>
       <c r="H132" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="I132" t="n">
-        <v>1.5255</v>
+        <v>1.5134</v>
       </c>
       <c r="J132" t="n">
-        <v>33.561</v>
+        <v>33.2948</v>
       </c>
     </row>
     <row r="133">
@@ -9555,10 +9555,10 @@
         <v>1.13</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3858</v>
+        <v>0.3861</v>
       </c>
       <c r="J133" t="n">
-        <v>8.4876</v>
+        <v>8.494199999999999</v>
       </c>
     </row>
     <row r="134">
@@ -9595,10 +9595,10 @@
         <v>1.07</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2287</v>
+        <v>0.229</v>
       </c>
       <c r="J134" t="n">
-        <v>5.0314</v>
+        <v>5.038</v>
       </c>
     </row>
     <row r="135">
@@ -9635,10 +9635,10 @@
         <v>1</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0336</v>
+        <v>-0.0332</v>
       </c>
       <c r="J135" t="n">
-        <v>-0.7392</v>
+        <v>-0.7304</v>
       </c>
     </row>
     <row r="136">
@@ -9675,10 +9675,10 @@
         <v>0.98</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.1349</v>
+        <v>-0.1345</v>
       </c>
       <c r="J136" t="n">
-        <v>-2.9678</v>
+        <v>-2.959</v>
       </c>
     </row>
     <row r="137">
@@ -9715,10 +9715,10 @@
         <v>1.86</v>
       </c>
       <c r="I137" t="n">
-        <v>1.2848</v>
+        <v>1.284</v>
       </c>
       <c r="J137" t="n">
-        <v>28.2656</v>
+        <v>28.248</v>
       </c>
     </row>
     <row r="138">
@@ -9752,13 +9752,13 @@
         <v>22</v>
       </c>
       <c r="H138" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1135</v>
+        <v>-0.1011</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.497</v>
+        <v>-2.2242</v>
       </c>
     </row>
     <row r="139">
@@ -9795,10 +9795,10 @@
         <v>0.84</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2141</v>
+        <v>-0.2142</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.7102</v>
+        <v>-4.7124</v>
       </c>
     </row>
     <row r="140">
@@ -9835,10 +9835,10 @@
         <v>0.84</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2141</v>
+        <v>-0.2142</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.7102</v>
+        <v>-4.7124</v>
       </c>
     </row>
     <row r="141">
@@ -9875,10 +9875,10 @@
         <v>0.65</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.395</v>
+        <v>-0.3952</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.69</v>
+        <v>-8.6944</v>
       </c>
     </row>
     <row r="142">
@@ -10512,13 +10512,13 @@
         <v>28</v>
       </c>
       <c r="H157" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="I157" t="n">
-        <v>1.3166</v>
+        <v>1.329</v>
       </c>
       <c r="J157" t="n">
-        <v>36.8648</v>
+        <v>37.212</v>
       </c>
     </row>
     <row r="158">
@@ -10555,10 +10555,10 @@
         <v>1.54</v>
       </c>
       <c r="I158" t="n">
-        <v>1.1458</v>
+        <v>1.1454</v>
       </c>
       <c r="J158" t="n">
-        <v>32.0824</v>
+        <v>32.0712</v>
       </c>
     </row>
     <row r="159">
@@ -10595,10 +10595,10 @@
         <v>1.34</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8212</v>
+        <v>0.8209</v>
       </c>
       <c r="J159" t="n">
-        <v>22.9936</v>
+        <v>22.9852</v>
       </c>
     </row>
     <row r="160">
@@ -10635,10 +10635,10 @@
         <v>1.09</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2736</v>
+        <v>0.2733</v>
       </c>
       <c r="J160" t="n">
-        <v>7.6608</v>
+        <v>7.6524</v>
       </c>
     </row>
     <row r="161">
@@ -10675,10 +10675,10 @@
         <v>0.67</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.9167</v>
+        <v>-0.9169</v>
       </c>
       <c r="J161" t="n">
-        <v>-25.6676</v>
+        <v>-25.6732</v>
       </c>
     </row>
     <row r="162">
@@ -11324,7 +11324,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11364,7 +11364,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15512,13 +15512,13 @@
         <v>30</v>
       </c>
       <c r="H282" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="I282" t="n">
-        <v>0.4998</v>
+        <v>0.4894</v>
       </c>
       <c r="J282" t="n">
-        <v>14.994</v>
+        <v>14.682</v>
       </c>
     </row>
     <row r="283">
@@ -15555,10 +15555,10 @@
         <v>1.37</v>
       </c>
       <c r="I283" t="n">
-        <v>0.4891</v>
+        <v>0.4894</v>
       </c>
       <c r="J283" t="n">
-        <v>14.673</v>
+        <v>14.682</v>
       </c>
     </row>
     <row r="284">
@@ -15595,10 +15595,10 @@
         <v>1.21</v>
       </c>
       <c r="I284" t="n">
-        <v>0.3106</v>
+        <v>0.3107</v>
       </c>
       <c r="J284" t="n">
-        <v>9.318</v>
+        <v>9.321</v>
       </c>
     </row>
     <row r="285">
@@ -15635,10 +15635,10 @@
         <v>1.11</v>
       </c>
       <c r="I285" t="n">
-        <v>0.1842</v>
+        <v>0.1843</v>
       </c>
       <c r="J285" t="n">
-        <v>5.526</v>
+        <v>5.529</v>
       </c>
     </row>
     <row r="286">
@@ -15675,10 +15675,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.1152</v>
+        <v>-0.1151</v>
       </c>
       <c r="J286" t="n">
-        <v>-3.456</v>
+        <v>-3.453</v>
       </c>
     </row>
     <row r="287">
@@ -15715,10 +15715,10 @@
         <v>0.92</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.1145</v>
+        <v>-0.1147</v>
       </c>
       <c r="J287" t="n">
-        <v>-3.435</v>
+        <v>-3.441</v>
       </c>
     </row>
     <row r="288">
@@ -15755,10 +15755,10 @@
         <v>0.88</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.1595</v>
+        <v>-0.1596</v>
       </c>
       <c r="J288" t="n">
-        <v>-4.785</v>
+        <v>-4.788</v>
       </c>
     </row>
     <row r="289">
@@ -15795,10 +15795,10 @@
         <v>0.86</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1801</v>
+        <v>-0.1802</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.403</v>
+        <v>-5.406</v>
       </c>
     </row>
     <row r="290">
@@ -15835,10 +15835,10 @@
         <v>0.86</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1801</v>
+        <v>-0.1802</v>
       </c>
       <c r="J290" t="n">
-        <v>-5.403</v>
+        <v>-5.406</v>
       </c>
     </row>
     <row r="291">
@@ -15872,13 +15872,13 @@
         <v>30</v>
       </c>
       <c r="H291" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.1903</v>
+        <v>-0.1802</v>
       </c>
       <c r="J291" t="n">
-        <v>-5.709</v>
+        <v>-5.406</v>
       </c>
     </row>
     <row r="292">
@@ -16112,7 +16112,7 @@
         <v>14</v>
       </c>
       <c r="H297" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="I297" t="n">
         <v>1.9372</v>
@@ -16155,10 +16155,10 @@
         <v>1.98</v>
       </c>
       <c r="I298" t="n">
-        <v>1.6164</v>
+        <v>1.6166</v>
       </c>
       <c r="J298" t="n">
-        <v>22.6296</v>
+        <v>22.6324</v>
       </c>
     </row>
     <row r="299">
@@ -16195,10 +16195,10 @@
         <v>1.67</v>
       </c>
       <c r="I299" t="n">
-        <v>1.2593</v>
+        <v>1.2594</v>
       </c>
       <c r="J299" t="n">
-        <v>17.6302</v>
+        <v>17.6316</v>
       </c>
     </row>
     <row r="300">
@@ -16235,10 +16235,10 @@
         <v>1.61</v>
       </c>
       <c r="I300" t="n">
-        <v>1.1877</v>
+        <v>1.1879</v>
       </c>
       <c r="J300" t="n">
-        <v>16.6278</v>
+        <v>16.6306</v>
       </c>
     </row>
     <row r="301">
@@ -16275,10 +16275,10 @@
         <v>0.79</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.7085</v>
+        <v>-0.7083</v>
       </c>
       <c r="J301" t="n">
-        <v>-9.919</v>
+        <v>-9.9162</v>
       </c>
     </row>
     <row r="302">
@@ -16512,13 +16512,13 @@
         <v>15</v>
       </c>
       <c r="H307" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="I307" t="n">
-        <v>1.7015</v>
+        <v>1.6905</v>
       </c>
       <c r="J307" t="n">
-        <v>25.5225</v>
+        <v>25.3575</v>
       </c>
     </row>
     <row r="308">
@@ -16555,10 +16555,10 @@
         <v>1.98</v>
       </c>
       <c r="I308" t="n">
-        <v>1.6223</v>
+        <v>1.6226</v>
       </c>
       <c r="J308" t="n">
-        <v>24.3345</v>
+        <v>24.339</v>
       </c>
     </row>
     <row r="309">
@@ -16595,10 +16595,10 @@
         <v>1.82</v>
       </c>
       <c r="I309" t="n">
-        <v>1.4381</v>
+        <v>1.4384</v>
       </c>
       <c r="J309" t="n">
-        <v>21.5715</v>
+        <v>21.576</v>
       </c>
     </row>
     <row r="310">
@@ -16635,10 +16635,10 @@
         <v>1.33</v>
       </c>
       <c r="I310" t="n">
-        <v>0.7551</v>
+        <v>0.7554</v>
       </c>
       <c r="J310" t="n">
-        <v>11.3265</v>
+        <v>11.331</v>
       </c>
     </row>
     <row r="311">
@@ -16675,10 +16675,10 @@
         <v>0.99</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.1566</v>
+        <v>-0.1564</v>
       </c>
       <c r="J311" t="n">
-        <v>-2.349</v>
+        <v>-2.346</v>
       </c>
     </row>
     <row r="312">
@@ -16915,10 +16915,10 @@
         <v>2.22</v>
       </c>
       <c r="I317" t="n">
-        <v>1.9267</v>
+        <v>1.9273</v>
       </c>
       <c r="J317" t="n">
-        <v>32.7539</v>
+        <v>32.7641</v>
       </c>
     </row>
     <row r="318">
@@ -16952,13 +16952,13 @@
         <v>17</v>
       </c>
       <c r="H318" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="I318" t="n">
-        <v>1.5214</v>
+        <v>1.5098</v>
       </c>
       <c r="J318" t="n">
-        <v>25.8638</v>
+        <v>25.6666</v>
       </c>
     </row>
     <row r="319">
@@ -16995,10 +16995,10 @@
         <v>1.13</v>
       </c>
       <c r="I319" t="n">
-        <v>0.3441</v>
+        <v>0.3444</v>
       </c>
       <c r="J319" t="n">
-        <v>5.8497</v>
+        <v>5.8548</v>
       </c>
     </row>
     <row r="320">
@@ -17035,10 +17035,10 @@
         <v>1.11</v>
       </c>
       <c r="I320" t="n">
-        <v>0.2939</v>
+        <v>0.2942</v>
       </c>
       <c r="J320" t="n">
-        <v>4.9963</v>
+        <v>5.0014</v>
       </c>
     </row>
     <row r="321">
@@ -17075,10 +17075,10 @@
         <v>1.02</v>
       </c>
       <c r="I321" t="n">
-        <v>0.025</v>
+        <v>0.0253</v>
       </c>
       <c r="J321" t="n">
-        <v>0.425</v>
+        <v>0.4301</v>
       </c>
     </row>
     <row r="322">
@@ -18284,7 +18284,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -18312,19 +18312,19 @@
         <v>24</v>
       </c>
       <c r="H352" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="I352" t="n">
-        <v>0.3637</v>
+        <v>0.3754</v>
       </c>
       <c r="J352" t="n">
-        <v>8.7288</v>
+        <v>9.009600000000001</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -18355,10 +18355,10 @@
         <v>1.24</v>
       </c>
       <c r="I353" t="n">
-        <v>0.3637</v>
+        <v>0.3633</v>
       </c>
       <c r="J353" t="n">
-        <v>8.7288</v>
+        <v>8.719200000000001</v>
       </c>
     </row>
     <row r="354">
@@ -18395,10 +18395,10 @@
         <v>1.15</v>
       </c>
       <c r="I354" t="n">
-        <v>0.2505</v>
+        <v>0.2502</v>
       </c>
       <c r="J354" t="n">
-        <v>6.012</v>
+        <v>6.0048</v>
       </c>
     </row>
     <row r="355">
@@ -18435,10 +18435,10 @@
         <v>0.83</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.2265</v>
+        <v>-0.2266</v>
       </c>
       <c r="J355" t="n">
-        <v>-5.436</v>
+        <v>-5.4384</v>
       </c>
     </row>
     <row r="356">
@@ -18475,10 +18475,10 @@
         <v>0.78</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.2763</v>
+        <v>-0.2765</v>
       </c>
       <c r="J356" t="n">
-        <v>-6.6312</v>
+        <v>-6.636</v>
       </c>
     </row>
     <row r="357">
@@ -18715,10 +18715,10 @@
         <v>1.03</v>
       </c>
       <c r="I362" t="n">
-        <v>0.108</v>
+        <v>0.1083</v>
       </c>
       <c r="J362" t="n">
-        <v>2.268</v>
+        <v>2.2743</v>
       </c>
     </row>
     <row r="363">
@@ -18755,10 +18755,10 @@
         <v>1.02</v>
       </c>
       <c r="I363" t="n">
-        <v>0.0809</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="J363" t="n">
-        <v>1.6989</v>
+        <v>1.7052</v>
       </c>
     </row>
     <row r="364">
@@ -18795,10 +18795,10 @@
         <v>0.99</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.0221</v>
+        <v>-0.0219</v>
       </c>
       <c r="J364" t="n">
-        <v>-0.4641</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="365">
@@ -18835,10 +18835,10 @@
         <v>0.91</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.1312</v>
+        <v>-0.131</v>
       </c>
       <c r="J365" t="n">
-        <v>-2.7552</v>
+        <v>-2.751</v>
       </c>
     </row>
     <row r="366">
@@ -18872,13 +18872,13 @@
         <v>21</v>
       </c>
       <c r="H366" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.2574</v>
+        <v>-0.267</v>
       </c>
       <c r="J366" t="n">
-        <v>-5.4054</v>
+        <v>-5.607</v>
       </c>
     </row>
     <row r="367">
@@ -20715,10 +20715,10 @@
         <v>1.35</v>
       </c>
       <c r="I412" t="n">
-        <v>0.8777</v>
+        <v>0.8783</v>
       </c>
       <c r="J412" t="n">
-        <v>26.331</v>
+        <v>26.349</v>
       </c>
     </row>
     <row r="413">
@@ -20755,10 +20755,10 @@
         <v>1.23</v>
       </c>
       <c r="I413" t="n">
-        <v>0.6263</v>
+        <v>0.6268</v>
       </c>
       <c r="J413" t="n">
-        <v>18.789</v>
+        <v>18.804</v>
       </c>
     </row>
     <row r="414">
@@ -20792,13 +20792,13 @@
         <v>30</v>
       </c>
       <c r="H414" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="I414" t="n">
-        <v>0.3488</v>
+        <v>0.3242</v>
       </c>
       <c r="J414" t="n">
-        <v>10.464</v>
+        <v>9.726000000000001</v>
       </c>
     </row>
     <row r="415">
@@ -20835,10 +20835,10 @@
         <v>1.09</v>
       </c>
       <c r="I415" t="n">
-        <v>0.2983</v>
+        <v>0.2986</v>
       </c>
       <c r="J415" t="n">
-        <v>8.949</v>
+        <v>8.958</v>
       </c>
     </row>
     <row r="416">
@@ -20875,10 +20875,10 @@
         <v>0.74</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.7428</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="J416" t="n">
-        <v>-22.284</v>
+        <v>-22.272</v>
       </c>
     </row>
     <row r="417">
@@ -21515,10 +21515,10 @@
         <v>1.5</v>
       </c>
       <c r="I432" t="n">
-        <v>0.6298</v>
+        <v>0.6301</v>
       </c>
       <c r="J432" t="n">
-        <v>13.8556</v>
+        <v>13.8622</v>
       </c>
     </row>
     <row r="433">
@@ -21555,10 +21555,10 @@
         <v>1.36</v>
       </c>
       <c r="I433" t="n">
-        <v>0.4823</v>
+        <v>0.4826</v>
       </c>
       <c r="J433" t="n">
-        <v>10.6106</v>
+        <v>10.6172</v>
       </c>
     </row>
     <row r="434">
@@ -21592,13 +21592,13 @@
         <v>22</v>
       </c>
       <c r="H434" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="I434" t="n">
-        <v>0.3709</v>
+        <v>0.3596</v>
       </c>
       <c r="J434" t="n">
-        <v>8.159800000000001</v>
+        <v>7.9112</v>
       </c>
     </row>
     <row r="435">
@@ -21635,10 +21635,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I435" t="n">
-        <v>-0.1129</v>
+        <v>-0.1128</v>
       </c>
       <c r="J435" t="n">
-        <v>-2.4838</v>
+        <v>-2.4816</v>
       </c>
     </row>
     <row r="436">
@@ -21675,10 +21675,10 @@
         <v>0.8</v>
       </c>
       <c r="I436" t="n">
-        <v>-0.2667</v>
+        <v>-0.2665</v>
       </c>
       <c r="J436" t="n">
-        <v>-5.8674</v>
+        <v>-5.863</v>
       </c>
     </row>
     <row r="437">
@@ -21715,10 +21715,10 @@
         <v>1.28</v>
       </c>
       <c r="I437" t="n">
-        <v>0.482</v>
+        <v>0.4806</v>
       </c>
       <c r="J437" t="n">
-        <v>10.604</v>
+        <v>10.5732</v>
       </c>
     </row>
     <row r="438">
@@ -21752,13 +21752,13 @@
         <v>22</v>
       </c>
       <c r="H438" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I438" t="n">
-        <v>-0.1126</v>
+        <v>-0.0881</v>
       </c>
       <c r="J438" t="n">
-        <v>-2.4772</v>
+        <v>-1.9382</v>
       </c>
     </row>
     <row r="439">
@@ -21795,10 +21795,10 @@
         <v>0.92</v>
       </c>
       <c r="I439" t="n">
-        <v>-0.1126</v>
+        <v>-0.1131</v>
       </c>
       <c r="J439" t="n">
-        <v>-2.4772</v>
+        <v>-2.4882</v>
       </c>
     </row>
     <row r="440">
@@ -21835,10 +21835,10 @@
         <v>0.62</v>
       </c>
       <c r="I440" t="n">
-        <v>-0.4062</v>
+        <v>-0.4066</v>
       </c>
       <c r="J440" t="n">
-        <v>-8.936400000000001</v>
+        <v>-8.9452</v>
       </c>
     </row>
     <row r="441">
@@ -21875,10 +21875,10 @@
         <v>0.54</v>
       </c>
       <c r="I441" t="n">
-        <v>-0.4766</v>
+        <v>-0.477</v>
       </c>
       <c r="J441" t="n">
-        <v>-10.4852</v>
+        <v>-10.494</v>
       </c>
     </row>
     <row r="442">
@@ -24315,10 +24315,10 @@
         <v>1.81</v>
       </c>
       <c r="I502" t="n">
-        <v>1.5122</v>
+        <v>1.5115</v>
       </c>
       <c r="J502" t="n">
-        <v>33.2684</v>
+        <v>33.253</v>
       </c>
     </row>
     <row r="503">
@@ -24355,10 +24355,10 @@
         <v>1.53</v>
       </c>
       <c r="I503" t="n">
-        <v>1.1448</v>
+        <v>1.1444</v>
       </c>
       <c r="J503" t="n">
-        <v>25.1856</v>
+        <v>25.1768</v>
       </c>
     </row>
     <row r="504">
@@ -24392,13 +24392,13 @@
         <v>22</v>
       </c>
       <c r="H504" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="I504" t="n">
-        <v>0.1038</v>
+        <v>0.1371</v>
       </c>
       <c r="J504" t="n">
-        <v>2.2836</v>
+        <v>3.0162</v>
       </c>
     </row>
     <row r="505">
@@ -24435,10 +24435,10 @@
         <v>0.85</v>
       </c>
       <c r="I505" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.5079</v>
       </c>
       <c r="J505" t="n">
-        <v>-11.1672</v>
+        <v>-11.1738</v>
       </c>
     </row>
     <row r="506">
@@ -24475,10 +24475,10 @@
         <v>0.79</v>
       </c>
       <c r="I506" t="n">
-        <v>-0.6485</v>
+        <v>-0.6489</v>
       </c>
       <c r="J506" t="n">
-        <v>-14.267</v>
+        <v>-14.2758</v>
       </c>
     </row>
     <row r="507">
@@ -24752,13 +24752,13 @@
         <v>16</v>
       </c>
       <c r="H513" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I513" t="n">
-        <v>1.0363</v>
+        <v>1.0225</v>
       </c>
       <c r="J513" t="n">
-        <v>16.5808</v>
+        <v>16.36</v>
       </c>
     </row>
     <row r="514">
@@ -24795,10 +24795,10 @@
         <v>1.33</v>
       </c>
       <c r="I514" t="n">
-        <v>0.774</v>
+        <v>0.7746</v>
       </c>
       <c r="J514" t="n">
-        <v>12.384</v>
+        <v>12.3936</v>
       </c>
     </row>
     <row r="515">
@@ -24835,10 +24835,10 @@
         <v>1.26</v>
       </c>
       <c r="I515" t="n">
-        <v>0.633</v>
+        <v>0.6335</v>
       </c>
       <c r="J515" t="n">
-        <v>10.128</v>
+        <v>10.136</v>
       </c>
     </row>
     <row r="516">
@@ -24872,13 +24872,13 @@
         <v>16</v>
       </c>
       <c r="H516" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="I516" t="n">
-        <v>-0.0193</v>
+        <v>-0.0785</v>
       </c>
       <c r="J516" t="n">
-        <v>-0.3088</v>
+        <v>-1.256</v>
       </c>
     </row>
     <row r="517">
@@ -24912,13 +24912,13 @@
         <v>16</v>
       </c>
       <c r="H517" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="I517" t="n">
-        <v>0.4272</v>
+        <v>0.4445</v>
       </c>
       <c r="J517" t="n">
-        <v>6.8352</v>
+        <v>7.112</v>
       </c>
     </row>
     <row r="518">
@@ -24955,10 +24955,10 @@
         <v>0.89</v>
       </c>
       <c r="I518" t="n">
-        <v>-0.1344</v>
+        <v>-0.1351</v>
       </c>
       <c r="J518" t="n">
-        <v>-2.1504</v>
+        <v>-2.1616</v>
       </c>
     </row>
     <row r="519">
@@ -24992,13 +24992,13 @@
         <v>16</v>
       </c>
       <c r="H519" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="I519" t="n">
-        <v>-0.2404</v>
+        <v>-0.2311</v>
       </c>
       <c r="J519" t="n">
-        <v>-3.8464</v>
+        <v>-3.6976</v>
       </c>
     </row>
     <row r="520">
@@ -25035,10 +25035,10 @@
         <v>0.67</v>
       </c>
       <c r="I520" t="n">
-        <v>-0.3502</v>
+        <v>-0.3506</v>
       </c>
       <c r="J520" t="n">
-        <v>-5.6032</v>
+        <v>-5.6096</v>
       </c>
     </row>
     <row r="521">
@@ -25075,10 +25075,10 @@
         <v>0.29</v>
       </c>
       <c r="I521" t="n">
-        <v>-0.6803</v>
+        <v>-0.6806</v>
       </c>
       <c r="J521" t="n">
-        <v>-10.8848</v>
+        <v>-10.8896</v>
       </c>
     </row>
     <row r="522">
@@ -25115,10 +25115,10 @@
         <v>1.79</v>
       </c>
       <c r="I522" t="n">
-        <v>1.4441</v>
+        <v>1.4445</v>
       </c>
       <c r="J522" t="n">
-        <v>25.9938</v>
+        <v>26.001</v>
       </c>
     </row>
     <row r="523">
@@ -25152,13 +25152,13 @@
         <v>18</v>
       </c>
       <c r="H523" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="I523" t="n">
-        <v>1.1667</v>
+        <v>1.154</v>
       </c>
       <c r="J523" t="n">
-        <v>21.0006</v>
+        <v>20.772</v>
       </c>
     </row>
     <row r="524">
@@ -25195,10 +25195,10 @@
         <v>1.3</v>
       </c>
       <c r="I524" t="n">
-        <v>0.7313</v>
+        <v>0.7316</v>
       </c>
       <c r="J524" t="n">
-        <v>13.1634</v>
+        <v>13.1688</v>
       </c>
     </row>
     <row r="525">
@@ -25235,10 +25235,10 @@
         <v>1.29</v>
       </c>
       <c r="I525" t="n">
-        <v>0.7114</v>
+        <v>0.7116</v>
       </c>
       <c r="J525" t="n">
-        <v>12.8052</v>
+        <v>12.8088</v>
       </c>
     </row>
     <row r="526">
@@ -25275,10 +25275,10 @@
         <v>0.9</v>
       </c>
       <c r="I526" t="n">
-        <v>-0.4074</v>
+        <v>-0.4071</v>
       </c>
       <c r="J526" t="n">
-        <v>-7.3332</v>
+        <v>-7.3278</v>
       </c>
     </row>
     <row r="527">
@@ -26112,7 +26112,7 @@
         <v>16</v>
       </c>
       <c r="H547" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="I547" t="n">
         <v>1.9372</v>
@@ -26155,10 +26155,10 @@
         <v>1.65</v>
       </c>
       <c r="I548" t="n">
-        <v>1.2512</v>
+        <v>1.2517</v>
       </c>
       <c r="J548" t="n">
-        <v>20.0192</v>
+        <v>20.0272</v>
       </c>
     </row>
     <row r="549">
@@ -26192,13 +26192,13 @@
         <v>16</v>
       </c>
       <c r="H549" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="I549" t="n">
-        <v>0.925</v>
+        <v>0.9075</v>
       </c>
       <c r="J549" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
     </row>
     <row r="550">
@@ -26235,10 +26235,10 @@
         <v>1.27</v>
       </c>
       <c r="I550" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6542</v>
       </c>
       <c r="J550" t="n">
-        <v>10.4592</v>
+        <v>10.4672</v>
       </c>
     </row>
     <row r="551">
@@ -26275,10 +26275,10 @@
         <v>0.83</v>
       </c>
       <c r="I551" t="n">
-        <v>-0.5974</v>
+        <v>-0.597</v>
       </c>
       <c r="J551" t="n">
-        <v>-9.558400000000001</v>
+        <v>-9.552</v>
       </c>
     </row>
     <row r="552">
@@ -27315,10 +27315,10 @@
         <v>2.24</v>
       </c>
       <c r="I577" t="n">
-        <v>1.6074</v>
+        <v>1.6082</v>
       </c>
       <c r="J577" t="n">
-        <v>38.5776</v>
+        <v>38.5968</v>
       </c>
     </row>
     <row r="578">
@@ -27352,13 +27352,13 @@
         <v>24</v>
       </c>
       <c r="H578" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="I578" t="n">
-        <v>-0.1564</v>
+        <v>-0.1676</v>
       </c>
       <c r="J578" t="n">
-        <v>-3.7536</v>
+        <v>-4.0224</v>
       </c>
     </row>
     <row r="579">
@@ -27395,10 +27395,10 @@
         <v>0.85</v>
       </c>
       <c r="I579" t="n">
-        <v>-0.2111</v>
+        <v>-0.211</v>
       </c>
       <c r="J579" t="n">
-        <v>-5.0664</v>
+        <v>-5.064</v>
       </c>
     </row>
     <row r="580">
@@ -27435,10 +27435,10 @@
         <v>0.85</v>
       </c>
       <c r="I580" t="n">
-        <v>-0.2111</v>
+        <v>-0.211</v>
       </c>
       <c r="J580" t="n">
-        <v>-5.0664</v>
+        <v>-5.064</v>
       </c>
     </row>
     <row r="581">
@@ -27475,10 +27475,10 @@
         <v>0.72</v>
       </c>
       <c r="I581" t="n">
-        <v>-0.3384</v>
+        <v>-0.3383</v>
       </c>
       <c r="J581" t="n">
-        <v>-8.121600000000001</v>
+        <v>-8.119199999999999</v>
       </c>
     </row>
     <row r="582">
@@ -31112,13 +31112,13 @@
         <v>20</v>
       </c>
       <c r="H672" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="I672" t="n">
-        <v>1.6315</v>
+        <v>1.6223</v>
       </c>
       <c r="J672" t="n">
-        <v>32.63</v>
+        <v>32.446</v>
       </c>
     </row>
     <row r="673">
@@ -31152,13 +31152,13 @@
         <v>20</v>
       </c>
       <c r="H673" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="I673" t="n">
-        <v>1.072</v>
+        <v>1.0452</v>
       </c>
       <c r="J673" t="n">
-        <v>21.44</v>
+        <v>20.904</v>
       </c>
     </row>
     <row r="674">
@@ -31195,10 +31195,10 @@
         <v>1.01</v>
       </c>
       <c r="I674" t="n">
-        <v>0.0224</v>
+        <v>0.0242</v>
       </c>
       <c r="J674" t="n">
-        <v>0.448</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="675">
@@ -31232,13 +31232,13 @@
         <v>20</v>
       </c>
       <c r="H675" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I675" t="n">
-        <v>-0.2411</v>
+        <v>-0.2699</v>
       </c>
       <c r="J675" t="n">
-        <v>-4.822</v>
+        <v>-5.398</v>
       </c>
     </row>
     <row r="676">
@@ -31272,13 +31272,13 @@
         <v>20</v>
       </c>
       <c r="H676" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="I676" t="n">
-        <v>-0.7189</v>
+        <v>-0.7393</v>
       </c>
       <c r="J676" t="n">
-        <v>-14.378</v>
+        <v>-14.786</v>
       </c>
     </row>
     <row r="677">
@@ -31312,13 +31312,13 @@
         <v>20</v>
       </c>
       <c r="H677" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I677" t="n">
-        <v>0.108</v>
+        <v>0.1592</v>
       </c>
       <c r="J677" t="n">
-        <v>2.16</v>
+        <v>3.184</v>
       </c>
     </row>
     <row r="678">
@@ -31352,19 +31352,19 @@
         <v>20</v>
       </c>
       <c r="H678" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="I678" t="n">
-        <v>-0.0571</v>
+        <v>-0.0434</v>
       </c>
       <c r="J678" t="n">
-        <v>-1.142</v>
+        <v>-0.868</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>alex666</t>
+          <t>esenthial</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -31395,16 +31395,16 @@
         <v>0.74</v>
       </c>
       <c r="I679" t="n">
-        <v>-0.2938</v>
+        <v>-0.2947</v>
       </c>
       <c r="J679" t="n">
-        <v>-5.876</v>
+        <v>-5.894</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>esenthial</t>
+          <t>alex666</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
@@ -31432,13 +31432,13 @@
         <v>20</v>
       </c>
       <c r="H680" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="I680" t="n">
-        <v>-0.3032</v>
+        <v>-0.2947</v>
       </c>
       <c r="J680" t="n">
-        <v>-6.064</v>
+        <v>-5.894</v>
       </c>
     </row>
     <row r="681">
@@ -31475,10 +31475,10 @@
         <v>0.71</v>
       </c>
       <c r="I681" t="n">
-        <v>-0.3218</v>
+        <v>-0.3227</v>
       </c>
       <c r="J681" t="n">
-        <v>-6.436</v>
+        <v>-6.454</v>
       </c>
     </row>
     <row r="682">
@@ -31915,10 +31915,10 @@
         <v>1.37</v>
       </c>
       <c r="I692" t="n">
-        <v>0.9024</v>
+        <v>0.9018</v>
       </c>
       <c r="J692" t="n">
-        <v>18.9504</v>
+        <v>18.9378</v>
       </c>
     </row>
     <row r="693">
@@ -31955,10 +31955,10 @@
         <v>1.21</v>
       </c>
       <c r="I693" t="n">
-        <v>0.572</v>
+        <v>0.5717</v>
       </c>
       <c r="J693" t="n">
-        <v>12.012</v>
+        <v>12.0057</v>
       </c>
     </row>
     <row r="694">
@@ -31995,10 +31995,10 @@
         <v>1.09</v>
       </c>
       <c r="I694" t="n">
-        <v>0.2906</v>
+        <v>0.2903</v>
       </c>
       <c r="J694" t="n">
-        <v>6.1026</v>
+        <v>6.0963</v>
       </c>
     </row>
     <row r="695">
@@ -32035,10 +32035,10 @@
         <v>1.08</v>
       </c>
       <c r="I695" t="n">
-        <v>0.2636</v>
+        <v>0.2633</v>
       </c>
       <c r="J695" t="n">
-        <v>5.5356</v>
+        <v>5.5293</v>
       </c>
     </row>
     <row r="696">
@@ -32072,13 +32072,13 @@
         <v>21</v>
       </c>
       <c r="H696" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I696" t="n">
-        <v>0.1451</v>
+        <v>0.1763</v>
       </c>
       <c r="J696" t="n">
-        <v>3.0471</v>
+        <v>3.7023</v>
       </c>
     </row>
     <row r="697">
